--- a/research/traditional_assets/database/data/portugal/portugal_household_products.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08592807841313595</v>
+        <v>0.08578317944846836</v>
       </c>
       <c r="C2">
-        <v>266.9680596758295</v>
+        <v>265.2150737953363</v>
       </c>
       <c r="D2">
-        <v>257.8980596758295</v>
+        <v>258.7980737953363</v>
       </c>
       <c r="E2">
-        <v>-88.3</v>
+        <v>-85.64699999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.653</v>
       </c>
       <c r="G2">
         <v>9.07</v>
@@ -1451,28 +1451,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1334459</v>
       </c>
       <c r="N2">
-        <v>17.59999999999999</v>
+        <v>17.46655409999999</v>
       </c>
       <c r="O2">
-        <v>3.695999999999999</v>
+        <v>3.667976360999998</v>
       </c>
       <c r="P2">
-        <v>13.904</v>
+        <v>13.798577739</v>
       </c>
       <c r="Q2">
-        <v>29.30399999999999</v>
+        <v>29.19857773899999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08592807841313595</v>
+        <v>0.08624829237219027</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6820163182859925</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>131.8886530047007</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08578317944846836</v>
+        <v>0.08563828048380077</v>
       </c>
       <c r="C3">
-        <v>265.2150737953363</v>
+        <v>263.4683916625123</v>
       </c>
       <c r="D3">
-        <v>258.7980737953363</v>
+        <v>259.7043916625123</v>
       </c>
       <c r="E3">
-        <v>-85.64699999999999</v>
+        <v>-82.994</v>
       </c>
       <c r="F3">
-        <v>2.653</v>
+        <v>5.306</v>
       </c>
       <c r="G3">
         <v>9.07</v>
@@ -1533,28 +1533,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M3">
-        <v>0.1334459</v>
+        <v>0.2668918</v>
       </c>
       <c r="N3">
-        <v>17.46655409999999</v>
+        <v>17.33310819999999</v>
       </c>
       <c r="O3">
-        <v>3.667976360999998</v>
+        <v>3.639952721999999</v>
       </c>
       <c r="P3">
-        <v>13.798577739</v>
+        <v>13.693155478</v>
       </c>
       <c r="Q3">
-        <v>29.19857773899999</v>
+        <v>29.093155478</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08624829237219027</v>
+        <v>0.08657504131000079</v>
       </c>
       <c r="T3">
-        <v>0.6820163182859925</v>
+        <v>0.6875257747920628</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>131.8886530047007</v>
+        <v>65.94432650235036</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08563828048380077</v>
+        <v>0.08549338151913317</v>
       </c>
       <c r="C4">
-        <v>263.4683916625123</v>
+        <v>261.728079737789</v>
       </c>
       <c r="D4">
-        <v>259.7043916625123</v>
+        <v>260.617079737789</v>
       </c>
       <c r="E4">
-        <v>-82.994</v>
+        <v>-80.34099999999999</v>
       </c>
       <c r="F4">
-        <v>5.306</v>
+        <v>7.959</v>
       </c>
       <c r="G4">
         <v>9.07</v>
@@ -1615,28 +1615,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M4">
-        <v>0.2668918</v>
+        <v>0.4003377</v>
       </c>
       <c r="N4">
-        <v>17.33310819999999</v>
+        <v>17.19966229999999</v>
       </c>
       <c r="O4">
-        <v>3.639952721999999</v>
+        <v>3.611929082999998</v>
       </c>
       <c r="P4">
-        <v>13.693155478</v>
+        <v>13.58773321699999</v>
       </c>
       <c r="Q4">
-        <v>29.093155478</v>
+        <v>28.987733217</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08657504131000079</v>
+        <v>0.08690852733931256</v>
       </c>
       <c r="T4">
-        <v>0.6875257747920628</v>
+        <v>0.6931488283394952</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.94432650235036</v>
+        <v>43.96288433490025</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08549338151913317</v>
+        <v>0.08534848255446562</v>
       </c>
       <c r="C5">
-        <v>261.728079737789</v>
+        <v>259.9942054191495</v>
       </c>
       <c r="D5">
-        <v>260.617079737789</v>
+        <v>261.5362054191495</v>
       </c>
       <c r="E5">
-        <v>-80.34099999999999</v>
+        <v>-77.688</v>
       </c>
       <c r="F5">
-        <v>7.959</v>
+        <v>10.612</v>
       </c>
       <c r="G5">
         <v>9.07</v>
@@ -1697,28 +1697,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M5">
-        <v>0.4003377</v>
+        <v>0.5337836</v>
       </c>
       <c r="N5">
-        <v>17.19966229999999</v>
+        <v>17.06621639999999</v>
       </c>
       <c r="O5">
-        <v>3.611929082999998</v>
+        <v>3.583905443999999</v>
       </c>
       <c r="P5">
-        <v>13.58773321699999</v>
+        <v>13.482310956</v>
       </c>
       <c r="Q5">
-        <v>28.987733217</v>
+        <v>28.882310956</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08690852733931256</v>
+        <v>0.08724896099423501</v>
       </c>
       <c r="T5">
-        <v>0.6931488283394952</v>
+        <v>0.6988890288358326</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.96288433490025</v>
+        <v>32.97216325117519</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08534848255446562</v>
+        <v>0.08520358358979802</v>
       </c>
       <c r="C6">
-        <v>259.9942054191495</v>
+        <v>258.2668370587201</v>
       </c>
       <c r="D6">
-        <v>261.5362054191495</v>
+        <v>262.4618370587201</v>
       </c>
       <c r="E6">
-        <v>-77.688</v>
+        <v>-75.035</v>
       </c>
       <c r="F6">
-        <v>10.612</v>
+        <v>13.265</v>
       </c>
       <c r="G6">
         <v>9.07</v>
@@ -1779,28 +1779,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M6">
-        <v>0.5337836</v>
+        <v>0.6672295</v>
       </c>
       <c r="N6">
-        <v>17.06621639999999</v>
+        <v>16.93277049999999</v>
       </c>
       <c r="O6">
-        <v>3.583905443999999</v>
+        <v>3.555881804999999</v>
       </c>
       <c r="P6">
-        <v>13.482310956</v>
+        <v>13.37688869499999</v>
       </c>
       <c r="Q6">
-        <v>28.882310956</v>
+        <v>28.776888695</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08724896099423501</v>
+        <v>0.0875965616734716</v>
       </c>
       <c r="T6">
-        <v>0.6988890288358326</v>
+        <v>0.7047500756584087</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.97216325117519</v>
+        <v>26.37773060094014</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08520358358979802</v>
+        <v>0.08505868462513043</v>
       </c>
       <c r="C7">
-        <v>258.2668370587201</v>
+        <v>256.5460439797133</v>
       </c>
       <c r="D7">
-        <v>262.4618370587201</v>
+        <v>263.3940439797133</v>
       </c>
       <c r="E7">
-        <v>-75.035</v>
+        <v>-72.38199999999999</v>
       </c>
       <c r="F7">
-        <v>13.265</v>
+        <v>15.918</v>
       </c>
       <c r="G7">
         <v>9.07</v>
@@ -1861,28 +1861,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M7">
-        <v>0.6672295</v>
+        <v>0.8006754000000001</v>
       </c>
       <c r="N7">
-        <v>16.93277049999999</v>
+        <v>16.79932459999999</v>
       </c>
       <c r="O7">
-        <v>3.555881804999999</v>
+        <v>3.527858165999999</v>
       </c>
       <c r="P7">
-        <v>13.37688869499999</v>
+        <v>13.271466434</v>
       </c>
       <c r="Q7">
-        <v>28.776888695</v>
+        <v>28.671466434</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0875965616734716</v>
+        <v>0.08795155811184088</v>
       </c>
       <c r="T7">
-        <v>0.7047500756584087</v>
+        <v>0.7107358256048693</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.37773060094014</v>
+        <v>21.98144216745012</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08505868462513043</v>
+        <v>0.08491378566046286</v>
       </c>
       <c r="C8">
-        <v>256.5460439797133</v>
+        <v>254.8318964937362</v>
       </c>
       <c r="D8">
-        <v>263.3940439797133</v>
+        <v>264.3328964937362</v>
       </c>
       <c r="E8">
-        <v>-72.38200000000001</v>
+        <v>-69.729</v>
       </c>
       <c r="F8">
-        <v>15.918</v>
+        <v>18.571</v>
       </c>
       <c r="G8">
         <v>9.07</v>
@@ -1943,28 +1943,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M8">
-        <v>0.8006753999999999</v>
+        <v>0.9341212999999998</v>
       </c>
       <c r="N8">
-        <v>16.79932459999999</v>
+        <v>16.66587869999999</v>
       </c>
       <c r="O8">
-        <v>3.527858165999999</v>
+        <v>3.499834526999999</v>
       </c>
       <c r="P8">
-        <v>13.271466434</v>
+        <v>13.16604417299999</v>
       </c>
       <c r="Q8">
-        <v>28.671466434</v>
+        <v>28.56604417299999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08795155811184088</v>
+        <v>0.08831418888221812</v>
       </c>
       <c r="T8">
-        <v>0.7107358256048693</v>
+        <v>0.7168503013566302</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.98144216745013</v>
+        <v>18.84123614352868</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08491378566046284</v>
+        <v>0.08476888669579526</v>
       </c>
       <c r="C9">
-        <v>254.8318964937363</v>
+        <v>253.1244659184681</v>
       </c>
       <c r="D9">
-        <v>264.3328964937363</v>
+        <v>265.2784659184681</v>
       </c>
       <c r="E9">
-        <v>-69.729</v>
+        <v>-67.07599999999999</v>
       </c>
       <c r="F9">
-        <v>18.571</v>
+        <v>21.224</v>
       </c>
       <c r="G9">
         <v>9.07</v>
@@ -2025,28 +2025,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M9">
-        <v>0.9341213</v>
+        <v>1.0675672</v>
       </c>
       <c r="N9">
-        <v>16.66587869999999</v>
+        <v>16.5324328</v>
       </c>
       <c r="O9">
-        <v>3.499834526999999</v>
+        <v>3.471810887999999</v>
       </c>
       <c r="P9">
-        <v>13.16604417299999</v>
+        <v>13.060621912</v>
       </c>
       <c r="Q9">
-        <v>28.56604417299999</v>
+        <v>28.460621912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08831418888221812</v>
+        <v>0.08868470293021224</v>
       </c>
       <c r="T9">
-        <v>0.7168503013566302</v>
+        <v>0.7230977004942988</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.84123614352868</v>
+        <v>16.48608162558759</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08476888669579526</v>
+        <v>0.08462398773112768</v>
       </c>
       <c r="C10">
-        <v>253.1244659184681</v>
+        <v>251.4238245957196</v>
       </c>
       <c r="D10">
-        <v>265.2784659184681</v>
+        <v>266.2308245957196</v>
       </c>
       <c r="E10">
-        <v>-67.07599999999999</v>
+        <v>-64.423</v>
       </c>
       <c r="F10">
-        <v>21.224</v>
+        <v>23.877</v>
       </c>
       <c r="G10">
         <v>9.07</v>
@@ -2107,28 +2107,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M10">
-        <v>1.0675672</v>
+        <v>1.2010131</v>
       </c>
       <c r="N10">
-        <v>16.5324328</v>
+        <v>16.39898689999999</v>
       </c>
       <c r="O10">
-        <v>3.471810887999999</v>
+        <v>3.443787248999998</v>
       </c>
       <c r="P10">
-        <v>13.060621912</v>
+        <v>12.955199651</v>
       </c>
       <c r="Q10">
-        <v>28.460621912</v>
+        <v>28.355199651</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08868470293021224</v>
+        <v>0.08906336014409635</v>
       </c>
       <c r="T10">
-        <v>0.7230977004942988</v>
+        <v>0.7294824051075207</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.48608162558759</v>
+        <v>14.65429477830008</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08462398773112768</v>
+        <v>0.0844790887664601</v>
       </c>
       <c r="C11">
-        <v>251.4238245957196</v>
+        <v>249.730045909883</v>
       </c>
       <c r="D11">
-        <v>266.2308245957196</v>
+        <v>267.190045909883</v>
       </c>
       <c r="E11">
-        <v>-64.423</v>
+        <v>-61.77</v>
       </c>
       <c r="F11">
-        <v>23.877</v>
+        <v>26.53</v>
       </c>
       <c r="G11">
         <v>9.07</v>
@@ -2189,28 +2189,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M11">
-        <v>1.2010131</v>
+        <v>1.334459</v>
       </c>
       <c r="N11">
-        <v>16.39898689999999</v>
+        <v>16.265541</v>
       </c>
       <c r="O11">
-        <v>3.443787248999998</v>
+        <v>3.415763609999999</v>
       </c>
       <c r="P11">
-        <v>12.955199651</v>
+        <v>12.84977739</v>
       </c>
       <c r="Q11">
-        <v>28.355199651</v>
+        <v>28.24977739</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08906336014409635</v>
+        <v>0.08945043196273345</v>
       </c>
       <c r="T11">
-        <v>0.7294824051075207</v>
+        <v>0.7360089920454808</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.65429477830008</v>
+        <v>13.18886530047008</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0844790887664601</v>
+        <v>0.08446453980179251</v>
       </c>
       <c r="C12">
-        <v>249.730045909883</v>
+        <v>247.1737410630546</v>
       </c>
       <c r="D12">
-        <v>267.190045909883</v>
+        <v>267.2867410630546</v>
       </c>
       <c r="E12">
-        <v>-61.77</v>
+        <v>-59.117</v>
       </c>
       <c r="F12">
-        <v>26.53</v>
+        <v>29.183</v>
       </c>
       <c r="G12">
         <v>9.07</v>
@@ -2271,45 +2271,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M12">
-        <v>1.334459</v>
+        <v>1.5116794</v>
       </c>
       <c r="N12">
-        <v>16.265541</v>
+        <v>16.0883206</v>
       </c>
       <c r="O12">
-        <v>3.415763609999999</v>
+        <v>3.378547325999999</v>
       </c>
       <c r="P12">
-        <v>12.84977739</v>
+        <v>12.709773274</v>
       </c>
       <c r="Q12">
-        <v>28.24977739</v>
+        <v>28.109773274</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08945043196273345</v>
+        <v>0.08984620202448595</v>
       </c>
       <c r="T12">
-        <v>0.7360089920454808</v>
+        <v>0.7426822438584513</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.21</v>
       </c>
       <c r="W12">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.18886530047007</v>
+        <v>11.64268031964979</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08446453980179251</v>
+        <v>0.08433149083712492</v>
       </c>
       <c r="C13">
-        <v>247.1737410630546</v>
+        <v>245.4082667742038</v>
       </c>
       <c r="D13">
-        <v>267.2867410630546</v>
+        <v>268.1742667742038</v>
       </c>
       <c r="E13">
-        <v>-59.117</v>
+        <v>-56.464</v>
       </c>
       <c r="F13">
-        <v>29.183</v>
+        <v>31.836</v>
       </c>
       <c r="G13">
         <v>9.07</v>
@@ -2353,28 +2353,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M13">
-        <v>1.5116794</v>
+        <v>1.6491048</v>
       </c>
       <c r="N13">
-        <v>16.0883206</v>
+        <v>15.95089519999999</v>
       </c>
       <c r="O13">
-        <v>3.378547325999999</v>
+        <v>3.349687991999999</v>
       </c>
       <c r="P13">
-        <v>12.709773274</v>
+        <v>12.60120720799999</v>
       </c>
       <c r="Q13">
-        <v>28.109773274</v>
+        <v>28.001207208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08984620202448595</v>
+        <v>0.09025096686036924</v>
       </c>
       <c r="T13">
-        <v>0.7426822438584513</v>
+        <v>0.7495071604853528</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.64268031964979</v>
+        <v>10.67245695967897</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08433149083712492</v>
+        <v>0.08419844187245734</v>
       </c>
       <c r="C14">
-        <v>245.4082667742038</v>
+        <v>243.6487061806085</v>
       </c>
       <c r="D14">
-        <v>268.1742667742038</v>
+        <v>269.0677061806085</v>
       </c>
       <c r="E14">
-        <v>-56.464</v>
+        <v>-53.81099999999999</v>
       </c>
       <c r="F14">
-        <v>31.836</v>
+        <v>34.489</v>
       </c>
       <c r="G14">
         <v>9.07</v>
@@ -2435,28 +2435,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M14">
-        <v>1.6491048</v>
+        <v>1.7865302</v>
       </c>
       <c r="N14">
-        <v>15.95089519999999</v>
+        <v>15.81346979999999</v>
       </c>
       <c r="O14">
-        <v>3.349687991999999</v>
+        <v>3.320828657999999</v>
       </c>
       <c r="P14">
-        <v>12.60120720799999</v>
+        <v>12.492641142</v>
       </c>
       <c r="Q14">
-        <v>28.001207208</v>
+        <v>27.892641142</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09025096686036924</v>
+        <v>0.09066503663500844</v>
       </c>
       <c r="T14">
-        <v>0.7495071604853528</v>
+        <v>0.7564889717473557</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.67245695967897</v>
+        <v>9.851498732011354</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08419844187245734</v>
+        <v>0.08425341290778973</v>
       </c>
       <c r="C15">
-        <v>243.6487061806085</v>
+        <v>240.6258485287495</v>
       </c>
       <c r="D15">
-        <v>269.0677061806085</v>
+        <v>268.6978485287495</v>
       </c>
       <c r="E15">
-        <v>-53.81099999999999</v>
+        <v>-51.15799999999999</v>
       </c>
       <c r="F15">
-        <v>34.489</v>
+        <v>37.142</v>
       </c>
       <c r="G15">
         <v>9.07</v>
@@ -2517,45 +2517,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M15">
-        <v>1.7865302</v>
+        <v>1.987097</v>
       </c>
       <c r="N15">
-        <v>15.81346979999999</v>
+        <v>15.61290299999999</v>
       </c>
       <c r="O15">
-        <v>3.320828657999999</v>
+        <v>3.278709629999998</v>
       </c>
       <c r="P15">
-        <v>12.492641142</v>
+        <v>12.33419337</v>
       </c>
       <c r="Q15">
-        <v>27.892641142</v>
+        <v>27.73419337</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09066503663500844</v>
+        <v>0.0910887359392904</v>
       </c>
       <c r="T15">
-        <v>0.7564889717473557</v>
+        <v>0.763633150713126</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.851498732011354</v>
+        <v>8.857141850649462</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08425341290778973</v>
+        <v>0.08413379394312218</v>
       </c>
       <c r="C16">
-        <v>240.6258485287495</v>
+        <v>238.7789771351286</v>
       </c>
       <c r="D16">
-        <v>268.6978485287495</v>
+        <v>269.5039771351286</v>
       </c>
       <c r="E16">
-        <v>-51.15799999999999</v>
+        <v>-48.50499999999999</v>
       </c>
       <c r="F16">
-        <v>37.142</v>
+        <v>39.79500000000001</v>
       </c>
       <c r="G16">
         <v>9.07</v>
@@ -2599,28 +2599,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M16">
-        <v>1.987097</v>
+        <v>2.129032500000001</v>
       </c>
       <c r="N16">
-        <v>15.61290299999999</v>
+        <v>15.47096749999999</v>
       </c>
       <c r="O16">
-        <v>3.278709629999998</v>
+        <v>3.248903174999998</v>
       </c>
       <c r="P16">
-        <v>12.33419337</v>
+        <v>12.22206432499999</v>
       </c>
       <c r="Q16">
-        <v>27.73419337</v>
+        <v>27.622064325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0910887359392904</v>
+        <v>0.09152240463896726</v>
       </c>
       <c r="T16">
-        <v>0.763633150713126</v>
+        <v>0.7709454280075027</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.857141850649462</v>
+        <v>8.26666572727283</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08413379394312218</v>
+        <v>0.08401417497845458</v>
       </c>
       <c r="C17">
-        <v>238.7789771351286</v>
+        <v>236.9369572787649</v>
       </c>
       <c r="D17">
-        <v>269.5039771351286</v>
+        <v>270.314957278765</v>
       </c>
       <c r="E17">
-        <v>-48.505</v>
+        <v>-45.852</v>
       </c>
       <c r="F17">
-        <v>39.795</v>
+        <v>42.448</v>
       </c>
       <c r="G17">
         <v>9.07</v>
@@ -2681,28 +2681,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M17">
-        <v>2.1290325</v>
+        <v>2.270968</v>
       </c>
       <c r="N17">
-        <v>15.47096749999999</v>
+        <v>15.32903199999999</v>
       </c>
       <c r="O17">
-        <v>3.248903174999998</v>
+        <v>3.219096719999999</v>
       </c>
       <c r="P17">
-        <v>12.22206432499999</v>
+        <v>12.10993527999999</v>
       </c>
       <c r="Q17">
-        <v>27.622064325</v>
+        <v>27.50993527999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09152240463896726</v>
+        <v>0.0919663987838745</v>
       </c>
       <c r="T17">
-        <v>0.7709454280075027</v>
+        <v>0.7784318071422216</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.26666572727283</v>
+        <v>7.74999911931828</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08401417497845458</v>
+        <v>0.08400199601378699</v>
       </c>
       <c r="C18">
-        <v>236.9369572787649</v>
+        <v>234.3668007959259</v>
       </c>
       <c r="D18">
-        <v>270.314957278765</v>
+        <v>270.3978007959259</v>
       </c>
       <c r="E18">
-        <v>-45.852</v>
+        <v>-43.19899999999999</v>
       </c>
       <c r="F18">
-        <v>42.448</v>
+        <v>45.10100000000001</v>
       </c>
       <c r="G18">
         <v>9.07</v>
@@ -2763,45 +2763,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M18">
-        <v>2.270968</v>
+        <v>2.4489843</v>
       </c>
       <c r="N18">
-        <v>15.32903199999999</v>
+        <v>15.15101569999999</v>
       </c>
       <c r="O18">
-        <v>3.219096719999999</v>
+        <v>3.181713296999999</v>
       </c>
       <c r="P18">
-        <v>12.10993527999999</v>
+        <v>11.969302403</v>
       </c>
       <c r="Q18">
-        <v>27.50993527999999</v>
+        <v>27.369302403</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0919663987838745</v>
+        <v>0.0924210915828759</v>
       </c>
       <c r="T18">
-        <v>0.7784318071422216</v>
+        <v>0.7860985809548857</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.74999911931828</v>
+        <v>7.186652850326559</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08400199601378699</v>
+        <v>0.0838886970491194</v>
       </c>
       <c r="C19">
-        <v>234.3668007959259</v>
+        <v>232.4869212065163</v>
       </c>
       <c r="D19">
-        <v>270.3978007959259</v>
+        <v>271.1709212065164</v>
       </c>
       <c r="E19">
-        <v>-43.19899999999999</v>
+        <v>-40.54599999999999</v>
       </c>
       <c r="F19">
-        <v>45.10100000000001</v>
+        <v>47.754</v>
       </c>
       <c r="G19">
         <v>9.07</v>
@@ -2845,28 +2845,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M19">
-        <v>2.4489843</v>
+        <v>2.5930422</v>
       </c>
       <c r="N19">
-        <v>15.15101569999999</v>
+        <v>15.0069578</v>
       </c>
       <c r="O19">
-        <v>3.181713296999999</v>
+        <v>3.151461137999999</v>
       </c>
       <c r="P19">
-        <v>11.969302403</v>
+        <v>11.855496662</v>
       </c>
       <c r="Q19">
-        <v>27.369302403</v>
+        <v>27.255496662</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0924210915828759</v>
+        <v>0.09288687445014562</v>
       </c>
       <c r="T19">
-        <v>0.7860985809548857</v>
+        <v>0.7939523492507853</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.186652850326559</v>
+        <v>6.787394358641751</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08388869704911942</v>
+        <v>0.08377539808445184</v>
       </c>
       <c r="C20">
-        <v>232.4869212065163</v>
+        <v>230.6114753000203</v>
       </c>
       <c r="D20">
-        <v>271.1709212065163</v>
+        <v>271.9484753000203</v>
       </c>
       <c r="E20">
-        <v>-40.546</v>
+        <v>-37.89299999999999</v>
       </c>
       <c r="F20">
-        <v>47.754</v>
+        <v>50.407</v>
       </c>
       <c r="G20">
         <v>9.07</v>
@@ -2927,28 +2927,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M20">
-        <v>2.5930422</v>
+        <v>2.7371001</v>
       </c>
       <c r="N20">
-        <v>15.0069578</v>
+        <v>14.8628999</v>
       </c>
       <c r="O20">
-        <v>3.151461137999999</v>
+        <v>3.121208978999999</v>
       </c>
       <c r="P20">
-        <v>11.855496662</v>
+        <v>11.741690921</v>
       </c>
       <c r="Q20">
-        <v>27.255496662</v>
+        <v>27.141690921</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09288687445014562</v>
+        <v>0.09336415812895288</v>
       </c>
       <c r="T20">
-        <v>0.7939523492507853</v>
+        <v>0.8020000377515222</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.787394358641752</v>
+        <v>6.430163076607974</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08377539808445184</v>
+        <v>0.08382009911978426</v>
       </c>
       <c r="C21">
-        <v>230.6114753000203</v>
+        <v>227.6511666933872</v>
       </c>
       <c r="D21">
-        <v>271.9484753000203</v>
+        <v>271.6411666933872</v>
       </c>
       <c r="E21">
-        <v>-37.89299999999999</v>
+        <v>-35.23999999999999</v>
       </c>
       <c r="F21">
-        <v>50.407</v>
+        <v>53.06</v>
       </c>
       <c r="G21">
         <v>9.07</v>
@@ -3009,45 +3009,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M21">
-        <v>2.7371001</v>
+        <v>2.934218</v>
       </c>
       <c r="N21">
-        <v>14.8628999</v>
+        <v>14.66578199999999</v>
       </c>
       <c r="O21">
-        <v>3.121208978999999</v>
+        <v>3.079814219999998</v>
       </c>
       <c r="P21">
-        <v>11.741690921</v>
+        <v>11.58596777999999</v>
       </c>
       <c r="Q21">
-        <v>27.141690921</v>
+        <v>26.98596778</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09336415812895288</v>
+        <v>0.09385337389973031</v>
       </c>
       <c r="T21">
-        <v>0.8020000377515222</v>
+        <v>0.8102489184647773</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.21</v>
       </c>
       <c r="W21">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.430163076607974</v>
+        <v>5.998191000123369</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08382009911978426</v>
+        <v>0.08371470015511666</v>
       </c>
       <c r="C22">
-        <v>227.6511666933872</v>
+        <v>225.7238734113897</v>
       </c>
       <c r="D22">
-        <v>271.6411666933872</v>
+        <v>272.3668734113897</v>
       </c>
       <c r="E22">
-        <v>-35.23999999999999</v>
+        <v>-32.58699999999999</v>
       </c>
       <c r="F22">
-        <v>53.06</v>
+        <v>55.71300000000001</v>
       </c>
       <c r="G22">
         <v>9.07</v>
@@ -3091,28 +3091,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M22">
-        <v>2.934218</v>
+        <v>3.0809289</v>
       </c>
       <c r="N22">
-        <v>14.66578199999999</v>
+        <v>14.51907109999999</v>
       </c>
       <c r="O22">
-        <v>3.079814219999998</v>
+        <v>3.049004930999999</v>
       </c>
       <c r="P22">
-        <v>11.58596777999999</v>
+        <v>11.470066169</v>
       </c>
       <c r="Q22">
-        <v>26.98596778</v>
+        <v>26.870066169</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09385337389973031</v>
+        <v>0.0943549748798945</v>
       </c>
       <c r="T22">
-        <v>0.8102489184647773</v>
+        <v>0.8187066316011528</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.998191000123369</v>
+        <v>5.712562857260352</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08371470015511666</v>
+        <v>0.08360930119044907</v>
       </c>
       <c r="C23">
-        <v>225.7238734113897</v>
+        <v>223.800468059897</v>
       </c>
       <c r="D23">
-        <v>272.3668734113897</v>
+        <v>273.096468059897</v>
       </c>
       <c r="E23">
-        <v>-32.587</v>
+        <v>-29.934</v>
       </c>
       <c r="F23">
-        <v>55.713</v>
+        <v>58.366</v>
       </c>
       <c r="G23">
         <v>9.07</v>
@@ -3173,28 +3173,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M23">
-        <v>3.0809289</v>
+        <v>3.2276398</v>
       </c>
       <c r="N23">
-        <v>14.51907109999999</v>
+        <v>14.37236019999999</v>
       </c>
       <c r="O23">
-        <v>3.049004930999999</v>
+        <v>3.018195641999998</v>
       </c>
       <c r="P23">
-        <v>11.470066169</v>
+        <v>11.354164558</v>
       </c>
       <c r="Q23">
-        <v>26.870066169</v>
+        <v>26.754164558</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0943549748798945</v>
+        <v>0.09486943742365264</v>
       </c>
       <c r="T23">
-        <v>0.8187066316011528</v>
+        <v>0.8273812091769226</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.712562857260353</v>
+        <v>5.452900909203064</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08360930119044907</v>
+        <v>0.08350390222578148</v>
       </c>
       <c r="C24">
-        <v>223.800468059897</v>
+        <v>221.8809819668622</v>
       </c>
       <c r="D24">
-        <v>273.096468059897</v>
+        <v>273.8299819668622</v>
       </c>
       <c r="E24">
-        <v>-29.934</v>
+        <v>-27.28099999999999</v>
       </c>
       <c r="F24">
-        <v>58.366</v>
+        <v>61.01900000000001</v>
       </c>
       <c r="G24">
         <v>9.07</v>
@@ -3255,28 +3255,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M24">
-        <v>3.2276398</v>
+        <v>3.3743507</v>
       </c>
       <c r="N24">
-        <v>14.37236019999999</v>
+        <v>14.22564929999999</v>
       </c>
       <c r="O24">
-        <v>3.018195641999998</v>
+        <v>2.987386352999998</v>
       </c>
       <c r="P24">
-        <v>11.354164558</v>
+        <v>11.238262947</v>
       </c>
       <c r="Q24">
-        <v>26.754164558</v>
+        <v>26.63826294699999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09486943742365264</v>
+        <v>0.09539726263088505</v>
       </c>
       <c r="T24">
-        <v>0.8273812091769226</v>
+        <v>0.8362811004559592</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.452900909203064</v>
+        <v>5.215818260976842</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08350390222578148</v>
+        <v>0.08339850326111389</v>
       </c>
       <c r="C25">
-        <v>221.8809819668622</v>
+        <v>219.9654467977215</v>
       </c>
       <c r="D25">
-        <v>273.8299819668622</v>
+        <v>274.5674467977215</v>
       </c>
       <c r="E25">
-        <v>-27.28099999999999</v>
+        <v>-24.62799999999999</v>
       </c>
       <c r="F25">
-        <v>61.01900000000001</v>
+        <v>63.67200000000001</v>
       </c>
       <c r="G25">
         <v>9.07</v>
@@ -3337,28 +3337,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M25">
-        <v>3.3743507</v>
+        <v>3.521061600000001</v>
       </c>
       <c r="N25">
-        <v>14.22564929999999</v>
+        <v>14.07893839999999</v>
       </c>
       <c r="O25">
-        <v>2.987386352999998</v>
+        <v>2.956577063999998</v>
       </c>
       <c r="P25">
-        <v>11.238262947</v>
+        <v>11.12236133599999</v>
       </c>
       <c r="Q25">
-        <v>26.63826294699999</v>
+        <v>26.522361336</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09539726263088505</v>
+        <v>0.09593897797514986</v>
       </c>
       <c r="T25">
-        <v>0.8362811004559592</v>
+        <v>0.8454151994002335</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.215818260976842</v>
+        <v>4.998492500102807</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08339850326111389</v>
+        <v>0.08329310429644632</v>
       </c>
       <c r="C26">
-        <v>219.9654467977215</v>
+        <v>218.053894559951</v>
       </c>
       <c r="D26">
-        <v>274.5674467977215</v>
+        <v>275.308894559951</v>
       </c>
       <c r="E26">
-        <v>-24.628</v>
+        <v>-21.97499999999999</v>
       </c>
       <c r="F26">
-        <v>63.672</v>
+        <v>66.325</v>
       </c>
       <c r="G26">
         <v>9.07</v>
@@ -3419,28 +3419,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M26">
-        <v>3.5210616</v>
+        <v>3.6677725</v>
       </c>
       <c r="N26">
-        <v>14.07893839999999</v>
+        <v>13.93222749999999</v>
       </c>
       <c r="O26">
-        <v>2.956577063999999</v>
+        <v>2.925767774999999</v>
       </c>
       <c r="P26">
-        <v>11.122361336</v>
+        <v>11.006459725</v>
       </c>
       <c r="Q26">
-        <v>26.522361336</v>
+        <v>26.406459725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09593897797514986</v>
+        <v>0.09649513906192841</v>
       </c>
       <c r="T26">
-        <v>0.8454151994002335</v>
+        <v>0.8547928743163551</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.998492500102809</v>
+        <v>4.798552800098696</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08329310429644632</v>
+        <v>0.08318770533177873</v>
       </c>
       <c r="C27">
-        <v>218.053894559951</v>
+        <v>216.1463576076981</v>
       </c>
       <c r="D27">
-        <v>275.308894559951</v>
+        <v>276.0543576076981</v>
       </c>
       <c r="E27">
-        <v>-21.97499999999999</v>
+        <v>-19.32199999999999</v>
       </c>
       <c r="F27">
-        <v>66.325</v>
+        <v>68.97800000000001</v>
       </c>
       <c r="G27">
         <v>9.07</v>
@@ -3501,28 +3501,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M27">
-        <v>3.6677725</v>
+        <v>3.814483400000001</v>
       </c>
       <c r="N27">
-        <v>13.93222749999999</v>
+        <v>13.78551659999999</v>
       </c>
       <c r="O27">
-        <v>2.925767774999999</v>
+        <v>2.894958485999999</v>
       </c>
       <c r="P27">
-        <v>11.006459725</v>
+        <v>10.890558114</v>
       </c>
       <c r="Q27">
-        <v>26.406459725</v>
+        <v>26.290558114</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09649513906192841</v>
+        <v>0.09706633152943071</v>
       </c>
       <c r="T27">
-        <v>0.8547928743163551</v>
+        <v>0.8644239999058855</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.798552800098696</v>
+        <v>4.613993077017977</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08318770533177873</v>
+        <v>0.08361555636711115</v>
       </c>
       <c r="C28">
-        <v>216.1463576076981</v>
+        <v>210.4920592743136</v>
       </c>
       <c r="D28">
-        <v>276.0543576076981</v>
+        <v>273.0530592743136</v>
       </c>
       <c r="E28">
-        <v>-19.32199999999999</v>
+        <v>-16.66899999999998</v>
       </c>
       <c r="F28">
-        <v>68.97800000000001</v>
+        <v>71.63100000000001</v>
       </c>
       <c r="G28">
         <v>9.07</v>
@@ -3583,45 +3583,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M28">
-        <v>3.814483400000001</v>
+        <v>4.140271800000001</v>
       </c>
       <c r="N28">
-        <v>13.78551659999999</v>
+        <v>13.45972819999999</v>
       </c>
       <c r="O28">
-        <v>2.894958485999999</v>
+        <v>2.826542921999998</v>
       </c>
       <c r="P28">
-        <v>10.890558114</v>
+        <v>10.633185278</v>
       </c>
       <c r="Q28">
-        <v>26.290558114</v>
+        <v>26.033185278</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09706633152943071</v>
+        <v>0.09765317310563171</v>
       </c>
       <c r="T28">
-        <v>0.8644239999058855</v>
+        <v>0.8743189919499236</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.21</v>
       </c>
       <c r="W28">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.613993077017977</v>
+        <v>4.250928646761787</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08361555636711115</v>
+        <v>0.08352990740244357</v>
       </c>
       <c r="C29">
-        <v>210.4920592743136</v>
+        <v>208.434635533146</v>
       </c>
       <c r="D29">
-        <v>273.0530592743136</v>
+        <v>273.648635533146</v>
       </c>
       <c r="E29">
-        <v>-16.66899999999998</v>
+        <v>-14.01599999999999</v>
       </c>
       <c r="F29">
-        <v>71.63100000000001</v>
+        <v>74.28400000000001</v>
       </c>
       <c r="G29">
         <v>9.07</v>
@@ -3665,28 +3665,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M29">
-        <v>4.140271800000001</v>
+        <v>4.293615200000001</v>
       </c>
       <c r="N29">
-        <v>13.45972819999999</v>
+        <v>13.30638479999999</v>
       </c>
       <c r="O29">
-        <v>2.826542921999998</v>
+        <v>2.794340807999999</v>
       </c>
       <c r="P29">
-        <v>10.633185278</v>
+        <v>10.512043992</v>
       </c>
       <c r="Q29">
-        <v>26.033185278</v>
+        <v>25.91204399199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09765317310563171</v>
+        <v>0.09825631583672717</v>
       </c>
       <c r="T29">
-        <v>0.8743189919499236</v>
+        <v>0.8844888448840738</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.250928646761787</v>
+        <v>4.099109766520296</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08352990740244357</v>
+        <v>0.08424610843777597</v>
       </c>
       <c r="C30">
-        <v>208.434635533146</v>
+        <v>200.8799360776988</v>
       </c>
       <c r="D30">
-        <v>273.648635533146</v>
+        <v>268.7469360776988</v>
       </c>
       <c r="E30">
-        <v>-14.01599999999999</v>
+        <v>-11.36299999999999</v>
       </c>
       <c r="F30">
-        <v>74.28400000000001</v>
+        <v>76.93700000000001</v>
       </c>
       <c r="G30">
         <v>9.07</v>
@@ -3747,45 +3747,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M30">
-        <v>4.293615200000001</v>
+        <v>4.716238100000001</v>
       </c>
       <c r="N30">
-        <v>13.30638479999999</v>
+        <v>12.88376189999999</v>
       </c>
       <c r="O30">
-        <v>2.794340807999999</v>
+        <v>2.705589998999999</v>
       </c>
       <c r="P30">
-        <v>10.512043992</v>
+        <v>10.17817190099999</v>
       </c>
       <c r="Q30">
-        <v>25.91204399199999</v>
+        <v>25.57817190099999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09825631583672717</v>
+        <v>0.09887644850390981</v>
       </c>
       <c r="T30">
-        <v>0.8844888448840738</v>
+        <v>0.8949451725487634</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.099109766520296</v>
+        <v>3.731787841669824</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08424610843777597</v>
+        <v>0.08418810947310837</v>
       </c>
       <c r="C31">
-        <v>200.8799360776988</v>
+        <v>198.6173386247413</v>
       </c>
       <c r="D31">
-        <v>268.7469360776988</v>
+        <v>269.1373386247413</v>
       </c>
       <c r="E31">
-        <v>-11.363</v>
+        <v>-8.709999999999994</v>
       </c>
       <c r="F31">
-        <v>76.937</v>
+        <v>79.59</v>
       </c>
       <c r="G31">
         <v>9.07</v>
@@ -3829,28 +3829,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M31">
-        <v>4.7162381</v>
+        <v>4.878867000000001</v>
       </c>
       <c r="N31">
-        <v>12.88376189999999</v>
+        <v>12.72113299999999</v>
       </c>
       <c r="O31">
-        <v>2.705589998999999</v>
+        <v>2.671437929999999</v>
       </c>
       <c r="P31">
-        <v>10.178171901</v>
+        <v>10.04969506999999</v>
       </c>
       <c r="Q31">
-        <v>25.578171901</v>
+        <v>25.44969507</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09887644850390981</v>
+        <v>0.09951429924729768</v>
       </c>
       <c r="T31">
-        <v>0.8949451725487634</v>
+        <v>0.9057002524324441</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.731787841669825</v>
+        <v>3.607394913614164</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08418810947310837</v>
+        <v>0.0848158305084408</v>
       </c>
       <c r="C32">
-        <v>198.6173386247413</v>
+        <v>191.7983839919763</v>
       </c>
       <c r="D32">
-        <v>269.1373386247413</v>
+        <v>264.9713839919763</v>
       </c>
       <c r="E32">
-        <v>-8.709999999999994</v>
+        <v>-6.056999999999988</v>
       </c>
       <c r="F32">
-        <v>79.59</v>
+        <v>82.24300000000001</v>
       </c>
       <c r="G32">
         <v>9.07</v>
@@ -3911,45 +3911,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M32">
-        <v>4.878867000000001</v>
+        <v>5.271776300000001</v>
       </c>
       <c r="N32">
-        <v>12.72113299999999</v>
+        <v>12.32822369999999</v>
       </c>
       <c r="O32">
-        <v>2.671437929999999</v>
+        <v>2.588926976999999</v>
       </c>
       <c r="P32">
-        <v>10.04969506999999</v>
+        <v>9.739296722999995</v>
       </c>
       <c r="Q32">
-        <v>25.44969507</v>
+        <v>25.13929672299999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09951429924729768</v>
+        <v>0.1001706384180301</v>
       </c>
       <c r="T32">
-        <v>0.9057002524324441</v>
+        <v>0.9167670737620288</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.607394913614164</v>
+        <v>3.338533161962884</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0848158305084408</v>
+        <v>0.08477995154377321</v>
       </c>
       <c r="C33">
-        <v>191.7983839919763</v>
+        <v>189.3800213624426</v>
       </c>
       <c r="D33">
-        <v>264.9713839919763</v>
+        <v>265.2060213624426</v>
       </c>
       <c r="E33">
-        <v>-6.056999999999988</v>
+        <v>-3.403999999999996</v>
       </c>
       <c r="F33">
-        <v>82.24300000000001</v>
+        <v>84.896</v>
       </c>
       <c r="G33">
         <v>9.07</v>
@@ -3993,28 +3993,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M33">
-        <v>5.271776300000001</v>
+        <v>5.441833600000001</v>
       </c>
       <c r="N33">
-        <v>12.32822369999999</v>
+        <v>12.15816639999999</v>
       </c>
       <c r="O33">
-        <v>2.588926976999999</v>
+        <v>2.553214943999999</v>
       </c>
       <c r="P33">
-        <v>9.739296722999995</v>
+        <v>9.604951455999995</v>
       </c>
       <c r="Q33">
-        <v>25.13929672299999</v>
+        <v>25.00495145599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1001706384180301</v>
+        <v>0.1008462816820194</v>
       </c>
       <c r="T33">
-        <v>0.9167670737620288</v>
+        <v>0.9281593898366011</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.338533161962884</v>
+        <v>3.234204000651544</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08477995154377321</v>
+        <v>0.08474407257910561</v>
       </c>
       <c r="C34">
-        <v>189.3800213624426</v>
+        <v>186.9620746532247</v>
       </c>
       <c r="D34">
-        <v>265.2060213624426</v>
+        <v>265.4410746532247</v>
       </c>
       <c r="E34">
-        <v>-3.403999999999996</v>
+        <v>-0.7509999999999906</v>
       </c>
       <c r="F34">
-        <v>84.896</v>
+        <v>87.54900000000001</v>
       </c>
       <c r="G34">
         <v>9.07</v>
@@ -4075,28 +4075,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M34">
-        <v>5.441833600000001</v>
+        <v>5.611890900000001</v>
       </c>
       <c r="N34">
-        <v>12.15816639999999</v>
+        <v>11.98810909999999</v>
       </c>
       <c r="O34">
-        <v>2.553214943999999</v>
+        <v>2.517502910999998</v>
       </c>
       <c r="P34">
-        <v>9.604951455999995</v>
+        <v>9.470606188999994</v>
       </c>
       <c r="Q34">
-        <v>25.00495145599999</v>
+        <v>24.87060618899999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1008462816820194</v>
+        <v>0.1015420934016502</v>
       </c>
       <c r="T34">
-        <v>0.9281593898366011</v>
+        <v>0.9398917750477278</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.234204000651544</v>
+        <v>3.136197818813618</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08474407257910561</v>
+        <v>0.08470819361443803</v>
       </c>
       <c r="C35">
-        <v>186.9620746532247</v>
+        <v>184.5445449711996</v>
       </c>
       <c r="D35">
-        <v>265.4410746532247</v>
+        <v>265.6765449711996</v>
       </c>
       <c r="E35">
-        <v>-0.7509999999999906</v>
+        <v>1.902000000000015</v>
       </c>
       <c r="F35">
-        <v>87.54900000000001</v>
+        <v>90.20200000000001</v>
       </c>
       <c r="G35">
         <v>9.07</v>
@@ -4157,28 +4157,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M35">
-        <v>5.611890900000001</v>
+        <v>5.781948200000001</v>
       </c>
       <c r="N35">
-        <v>11.98810909999999</v>
+        <v>11.81805179999999</v>
       </c>
       <c r="O35">
-        <v>2.517502910999998</v>
+        <v>2.481790877999998</v>
       </c>
       <c r="P35">
-        <v>9.470606188999994</v>
+        <v>9.336260921999994</v>
       </c>
       <c r="Q35">
-        <v>24.87060618899999</v>
+        <v>24.73626092199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1015420934016502</v>
+        <v>0.1022589903249061</v>
       </c>
       <c r="T35">
-        <v>0.9398917750477278</v>
+        <v>0.9519796870834343</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.136197818813618</v>
+        <v>3.04395670649557</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08470819361443803</v>
+        <v>0.08682901464977046</v>
       </c>
       <c r="C36">
-        <v>184.5445449711996</v>
+        <v>168.6545454640539</v>
       </c>
       <c r="D36">
-        <v>265.6765449711996</v>
+        <v>252.4395454640539</v>
       </c>
       <c r="E36">
-        <v>1.902000000000015</v>
+        <v>4.555000000000021</v>
       </c>
       <c r="F36">
-        <v>90.20200000000001</v>
+        <v>92.85500000000002</v>
       </c>
       <c r="G36">
         <v>9.07</v>
@@ -4239,45 +4239,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M36">
-        <v>5.781948200000001</v>
+        <v>6.676274500000002</v>
       </c>
       <c r="N36">
-        <v>11.81805179999999</v>
+        <v>10.92372549999999</v>
       </c>
       <c r="O36">
-        <v>2.481790877999998</v>
+        <v>2.293982354999998</v>
       </c>
       <c r="P36">
-        <v>9.336260921999994</v>
+        <v>8.629743144999994</v>
       </c>
       <c r="Q36">
-        <v>24.73626092199999</v>
+        <v>24.02974314499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1022589903249061</v>
+        <v>0.1029979456150315</v>
       </c>
       <c r="T36">
-        <v>0.9519796870834343</v>
+        <v>0.9644395348740854</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.04395670649557</v>
+        <v>2.636200773350465</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08682901464977046</v>
+        <v>0.08685475568510287</v>
       </c>
       <c r="C37">
-        <v>168.6545454640539</v>
+        <v>165.848981077801</v>
       </c>
       <c r="D37">
-        <v>252.4395454640539</v>
+        <v>252.286981077801</v>
       </c>
       <c r="E37">
-        <v>4.555000000000021</v>
+        <v>7.208000000000013</v>
       </c>
       <c r="F37">
-        <v>92.85500000000002</v>
+        <v>95.50800000000001</v>
       </c>
       <c r="G37">
         <v>9.07</v>
@@ -4321,28 +4321,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M37">
-        <v>6.676274500000002</v>
+        <v>6.867025200000001</v>
       </c>
       <c r="N37">
-        <v>10.92372549999999</v>
+        <v>10.73297479999999</v>
       </c>
       <c r="O37">
-        <v>2.293982354999998</v>
+        <v>2.253924707999999</v>
       </c>
       <c r="P37">
-        <v>8.629743144999994</v>
+        <v>8.479050091999994</v>
       </c>
       <c r="Q37">
-        <v>24.02974314499999</v>
+        <v>23.87905009199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1029979456150315</v>
+        <v>0.1037599932579732</v>
       </c>
       <c r="T37">
-        <v>0.9644395348740854</v>
+        <v>0.9772887529081944</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.636200773350465</v>
+        <v>2.56297297409073</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08685475568510287</v>
+        <v>0.08802046672043529</v>
       </c>
       <c r="C38">
-        <v>165.8489810778011</v>
+        <v>156.4750566798523</v>
       </c>
       <c r="D38">
-        <v>252.286981077801</v>
+        <v>245.5660566798524</v>
       </c>
       <c r="E38">
-        <v>7.207999999999998</v>
+        <v>9.861000000000004</v>
       </c>
       <c r="F38">
-        <v>95.508</v>
+        <v>98.161</v>
       </c>
       <c r="G38">
         <v>9.07</v>
@@ -4403,45 +4403,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M38">
-        <v>6.8670252</v>
+        <v>7.440603800000001</v>
       </c>
       <c r="N38">
-        <v>10.73297479999999</v>
+        <v>10.15939619999999</v>
       </c>
       <c r="O38">
-        <v>2.253924707999999</v>
+        <v>2.133473201999998</v>
       </c>
       <c r="P38">
-        <v>8.479050091999994</v>
+        <v>8.025922997999995</v>
       </c>
       <c r="Q38">
-        <v>23.87905009199999</v>
+        <v>23.425922998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1037599932579732</v>
+        <v>0.1045462328895798</v>
       </c>
       <c r="T38">
-        <v>0.9772887529081943</v>
+        <v>0.9905458826259258</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.21</v>
       </c>
       <c r="W38">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.562972974090731</v>
+        <v>2.365399431696658</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08802046672043529</v>
+        <v>0.08807701775576771</v>
       </c>
       <c r="C39">
-        <v>156.4750566798523</v>
+        <v>153.505106314811</v>
       </c>
       <c r="D39">
-        <v>245.5660566798524</v>
+        <v>245.249106314811</v>
       </c>
       <c r="E39">
-        <v>9.861000000000004</v>
+        <v>12.51400000000001</v>
       </c>
       <c r="F39">
-        <v>98.161</v>
+        <v>100.814</v>
       </c>
       <c r="G39">
         <v>9.07</v>
@@ -4485,28 +4485,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M39">
-        <v>7.440603800000001</v>
+        <v>7.641701200000001</v>
       </c>
       <c r="N39">
-        <v>10.15939619999999</v>
+        <v>9.958298799999994</v>
       </c>
       <c r="O39">
-        <v>2.133473201999998</v>
+        <v>2.091242747999999</v>
       </c>
       <c r="P39">
-        <v>8.025922997999995</v>
+        <v>7.867056051999995</v>
       </c>
       <c r="Q39">
-        <v>23.425922998</v>
+        <v>23.26705605199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1045462328895798</v>
+        <v>0.1053578350899479</v>
       </c>
       <c r="T39">
-        <v>0.9905458826259258</v>
+        <v>1.004230661689391</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.365399431696658</v>
+        <v>2.303152078230957</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08807701775576771</v>
+        <v>0.08813356879110013</v>
       </c>
       <c r="C40">
-        <v>153.505106314811</v>
+        <v>150.5359730662927</v>
       </c>
       <c r="D40">
-        <v>245.249106314811</v>
+        <v>244.9329730662927</v>
       </c>
       <c r="E40">
-        <v>12.51400000000001</v>
+        <v>15.16700000000002</v>
       </c>
       <c r="F40">
-        <v>100.814</v>
+        <v>103.467</v>
       </c>
       <c r="G40">
         <v>9.07</v>
@@ -4567,28 +4567,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M40">
-        <v>7.641701200000001</v>
+        <v>7.842798600000002</v>
       </c>
       <c r="N40">
-        <v>9.958298799999994</v>
+        <v>9.757201399999992</v>
       </c>
       <c r="O40">
-        <v>2.091242747999999</v>
+        <v>2.049012293999998</v>
       </c>
       <c r="P40">
-        <v>7.867056051999995</v>
+        <v>7.708189105999994</v>
       </c>
       <c r="Q40">
-        <v>23.26705605199999</v>
+        <v>23.10818910599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1053578350899479</v>
+        <v>0.1061960471985248</v>
       </c>
       <c r="T40">
-        <v>1.004230661689391</v>
+        <v>1.018364122033625</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.303152078230957</v>
+        <v>2.244096896737855</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08813356879110013</v>
+        <v>0.08819011982643254</v>
       </c>
       <c r="C41">
-        <v>150.5359730662927</v>
+        <v>147.5676537785044</v>
       </c>
       <c r="D41">
-        <v>244.9329730662927</v>
+        <v>244.6176537785044</v>
       </c>
       <c r="E41">
-        <v>15.16700000000002</v>
+        <v>17.82000000000001</v>
       </c>
       <c r="F41">
-        <v>103.467</v>
+        <v>106.12</v>
       </c>
       <c r="G41">
         <v>9.07</v>
@@ -4649,28 +4649,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M41">
-        <v>7.842798600000002</v>
+        <v>8.043896</v>
       </c>
       <c r="N41">
-        <v>9.757201399999992</v>
+        <v>9.556103999999994</v>
       </c>
       <c r="O41">
-        <v>2.049012293999998</v>
+        <v>2.006781839999999</v>
       </c>
       <c r="P41">
-        <v>7.708189105999994</v>
+        <v>7.549322159999996</v>
       </c>
       <c r="Q41">
-        <v>23.10818910599999</v>
+        <v>22.94932215999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1061960471985248</v>
+        <v>0.1070621997107209</v>
       </c>
       <c r="T41">
-        <v>1.018364122033625</v>
+        <v>1.032968697722667</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.244096896737855</v>
+        <v>2.187994474319408</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08819011982643254</v>
+        <v>0.08824667086176494</v>
       </c>
       <c r="C42">
-        <v>147.5676537785044</v>
+        <v>144.6001453118827</v>
       </c>
       <c r="D42">
-        <v>244.6176537785044</v>
+        <v>244.3031453118828</v>
       </c>
       <c r="E42">
-        <v>17.82000000000001</v>
+        <v>20.47300000000001</v>
       </c>
       <c r="F42">
-        <v>106.12</v>
+        <v>108.773</v>
       </c>
       <c r="G42">
         <v>9.07</v>
@@ -4731,28 +4731,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M42">
-        <v>8.043896</v>
+        <v>8.244993400000002</v>
       </c>
       <c r="N42">
-        <v>9.556103999999994</v>
+        <v>9.355006599999992</v>
       </c>
       <c r="O42">
-        <v>2.006781839999999</v>
+        <v>1.964551385999998</v>
       </c>
       <c r="P42">
-        <v>7.549322159999996</v>
+        <v>7.390455213999994</v>
       </c>
       <c r="Q42">
-        <v>22.94932215999999</v>
+        <v>22.79045521399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1070621997107209</v>
+        <v>0.1079577133250253</v>
       </c>
       <c r="T42">
-        <v>1.032968697722667</v>
+        <v>1.048068343774049</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.187994474319408</v>
+        <v>2.134628755433569</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08824667086176494</v>
+        <v>0.08830322189709736</v>
       </c>
       <c r="C43">
-        <v>144.6001453118827</v>
+        <v>141.6334445429897</v>
       </c>
       <c r="D43">
-        <v>244.3031453118828</v>
+        <v>243.9894445429897</v>
       </c>
       <c r="E43">
-        <v>20.47300000000001</v>
+        <v>23.12600000000002</v>
       </c>
       <c r="F43">
-        <v>108.773</v>
+        <v>111.426</v>
       </c>
       <c r="G43">
         <v>9.07</v>
@@ -4813,28 +4813,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M43">
-        <v>8.244993400000002</v>
+        <v>8.446090800000002</v>
       </c>
       <c r="N43">
-        <v>9.355006599999992</v>
+        <v>9.153909199999992</v>
       </c>
       <c r="O43">
-        <v>1.964551385999998</v>
+        <v>1.922320931999998</v>
       </c>
       <c r="P43">
-        <v>7.390455213999994</v>
+        <v>7.231588267999994</v>
       </c>
       <c r="Q43">
-        <v>22.79045521399999</v>
+        <v>22.63158826799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1079577133250253</v>
+        <v>0.1088841067191334</v>
       </c>
       <c r="T43">
-        <v>1.048068343774049</v>
+        <v>1.063688667275479</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.134628755433569</v>
+        <v>2.083804261256579</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08830322189709736</v>
+        <v>0.08835977293242978</v>
       </c>
       <c r="C44">
-        <v>141.6334445429897</v>
+        <v>138.6675483644099</v>
       </c>
       <c r="D44">
-        <v>243.9894445429897</v>
+        <v>243.6765483644099</v>
       </c>
       <c r="E44">
-        <v>23.126</v>
+        <v>25.77900000000001</v>
       </c>
       <c r="F44">
-        <v>111.426</v>
+        <v>114.079</v>
       </c>
       <c r="G44">
         <v>9.07</v>
@@ -4895,28 +4895,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M44">
-        <v>8.4460908</v>
+        <v>8.6471882</v>
       </c>
       <c r="N44">
-        <v>9.153909199999994</v>
+        <v>8.952811799999994</v>
       </c>
       <c r="O44">
-        <v>1.922320931999999</v>
+        <v>1.880090477999999</v>
       </c>
       <c r="P44">
-        <v>7.231588267999995</v>
+        <v>7.072721321999995</v>
       </c>
       <c r="Q44">
-        <v>22.63158826799999</v>
+        <v>22.47272132199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1088841067191334</v>
+        <v>0.1098430051446136</v>
       </c>
       <c r="T44">
-        <v>1.063688667275479</v>
+        <v>1.079857072303275</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.08380426125658</v>
+        <v>2.03534369704131</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08835977293242978</v>
+        <v>0.09335224396776221</v>
       </c>
       <c r="C45">
-        <v>138.6675483644099</v>
+        <v>111.2324044705752</v>
       </c>
       <c r="D45">
-        <v>243.6765483644099</v>
+        <v>218.8944044705752</v>
       </c>
       <c r="E45">
-        <v>25.77900000000001</v>
+        <v>28.432</v>
       </c>
       <c r="F45">
-        <v>114.079</v>
+        <v>116.732</v>
       </c>
       <c r="G45">
         <v>9.07</v>
@@ -4977,45 +4977,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M45">
-        <v>8.6471882</v>
+        <v>10.50588</v>
       </c>
       <c r="N45">
-        <v>8.952811799999994</v>
+        <v>7.094119999999995</v>
       </c>
       <c r="O45">
-        <v>1.880090477999999</v>
+        <v>1.489765199999999</v>
       </c>
       <c r="P45">
-        <v>7.072721321999995</v>
+        <v>5.604354799999996</v>
       </c>
       <c r="Q45">
-        <v>22.47272132199999</v>
+        <v>21.00435479999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1098430051446136</v>
+        <v>0.1108361499424325</v>
       </c>
       <c r="T45">
-        <v>1.079857072303275</v>
+        <v>1.096602920367778</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.21</v>
       </c>
       <c r="W45">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.03534369704131</v>
+        <v>1.675252334882941</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09335224396776221</v>
+        <v>0.09352097500309461</v>
       </c>
       <c r="C46">
-        <v>111.2324044705752</v>
+        <v>107.8295982815649</v>
       </c>
       <c r="D46">
-        <v>218.8944044705752</v>
+        <v>218.1445982815649</v>
       </c>
       <c r="E46">
-        <v>28.432</v>
+        <v>31.08500000000001</v>
       </c>
       <c r="F46">
-        <v>116.732</v>
+        <v>119.385</v>
       </c>
       <c r="G46">
         <v>9.07</v>
@@ -5059,28 +5059,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M46">
-        <v>10.50588</v>
+        <v>10.74465</v>
       </c>
       <c r="N46">
-        <v>7.094119999999995</v>
+        <v>6.855349999999994</v>
       </c>
       <c r="O46">
-        <v>1.489765199999999</v>
+        <v>1.439623499999999</v>
       </c>
       <c r="P46">
-        <v>5.604354799999996</v>
+        <v>5.415726499999995</v>
       </c>
       <c r="Q46">
-        <v>21.00435479999999</v>
+        <v>20.8157265</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1108361499424325</v>
+        <v>0.1118654090965356</v>
       </c>
       <c r="T46">
-        <v>1.096602920367778</v>
+        <v>1.113957708361899</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.675252334882941</v>
+        <v>1.638024505218876</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09352097500309461</v>
+        <v>0.09368970603842701</v>
       </c>
       <c r="C47">
-        <v>107.8295982815649</v>
+        <v>104.4319113653949</v>
       </c>
       <c r="D47">
-        <v>218.1445982815649</v>
+        <v>217.3999113653949</v>
       </c>
       <c r="E47">
-        <v>31.08500000000001</v>
+        <v>33.73800000000001</v>
       </c>
       <c r="F47">
-        <v>119.385</v>
+        <v>122.038</v>
       </c>
       <c r="G47">
         <v>9.07</v>
@@ -5141,28 +5141,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M47">
-        <v>10.74465</v>
+        <v>10.98342</v>
       </c>
       <c r="N47">
-        <v>6.855349999999994</v>
+        <v>6.616579999999994</v>
       </c>
       <c r="O47">
-        <v>1.439623499999999</v>
+        <v>1.389481799999999</v>
       </c>
       <c r="P47">
-        <v>5.415726499999995</v>
+        <v>5.227098199999995</v>
       </c>
       <c r="Q47">
-        <v>20.8157265</v>
+        <v>20.6270982</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1118654090965356</v>
+        <v>0.11293278896005</v>
       </c>
       <c r="T47">
-        <v>1.113957708361899</v>
+        <v>1.131955266281728</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.638024505218876</v>
+        <v>1.602415276844552</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09368970603842701</v>
+        <v>0.09385843707375943</v>
       </c>
       <c r="C48">
-        <v>104.4319113653949</v>
+        <v>101.0392914729726</v>
       </c>
       <c r="D48">
-        <v>217.3999113653949</v>
+        <v>216.6602914729726</v>
       </c>
       <c r="E48">
-        <v>33.73800000000001</v>
+        <v>36.39100000000002</v>
       </c>
       <c r="F48">
-        <v>122.038</v>
+        <v>124.691</v>
       </c>
       <c r="G48">
         <v>9.07</v>
@@ -5223,28 +5223,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M48">
-        <v>10.98342</v>
+        <v>11.22219</v>
       </c>
       <c r="N48">
-        <v>6.616579999999994</v>
+        <v>6.377809999999993</v>
       </c>
       <c r="O48">
-        <v>1.389481799999999</v>
+        <v>1.339340099999998</v>
       </c>
       <c r="P48">
-        <v>5.227098199999995</v>
+        <v>5.038469899999995</v>
       </c>
       <c r="Q48">
-        <v>20.6270982</v>
+        <v>20.43846989999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.11293278896005</v>
+        <v>0.1140404473089801</v>
       </c>
       <c r="T48">
-        <v>1.131955266281728</v>
+        <v>1.150631977330608</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.602415276844552</v>
+        <v>1.56832133478403</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09385843707375943</v>
+        <v>0.09402716810909184</v>
       </c>
       <c r="C49">
-        <v>101.0392914729726</v>
+        <v>97.65168706382477</v>
       </c>
       <c r="D49">
-        <v>216.6602914729726</v>
+        <v>215.9256870638248</v>
       </c>
       <c r="E49">
-        <v>36.39100000000002</v>
+        <v>39.04400000000003</v>
       </c>
       <c r="F49">
-        <v>124.691</v>
+        <v>127.344</v>
       </c>
       <c r="G49">
         <v>9.07</v>
@@ -5305,28 +5305,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M49">
-        <v>11.22219</v>
+        <v>11.46096</v>
       </c>
       <c r="N49">
-        <v>6.377809999999993</v>
+        <v>6.139039999999993</v>
       </c>
       <c r="O49">
-        <v>1.339340099999998</v>
+        <v>1.289198399999998</v>
       </c>
       <c r="P49">
-        <v>5.038469899999995</v>
+        <v>4.849841599999994</v>
       </c>
       <c r="Q49">
-        <v>20.43846989999999</v>
+        <v>20.2498416</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1140404473089801</v>
+        <v>0.1151907079020997</v>
       </c>
       <c r="T49">
-        <v>1.150631977330608</v>
+        <v>1.170027023419829</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.56832133478403</v>
+        <v>1.535647973642696</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09402716810909184</v>
+        <v>0.09419589914442425</v>
       </c>
       <c r="C50">
-        <v>97.6516870638248</v>
+        <v>94.26904729412496</v>
       </c>
       <c r="D50">
-        <v>215.9256870638248</v>
+        <v>215.196047294125</v>
       </c>
       <c r="E50">
-        <v>39.044</v>
+        <v>41.69700000000002</v>
       </c>
       <c r="F50">
-        <v>127.344</v>
+        <v>129.997</v>
       </c>
       <c r="G50">
         <v>9.07</v>
@@ -5387,28 +5387,28 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M50">
-        <v>11.46096</v>
+        <v>11.69973</v>
       </c>
       <c r="N50">
-        <v>6.139039999999996</v>
+        <v>5.900269999999994</v>
       </c>
       <c r="O50">
-        <v>1.289198399999999</v>
+        <v>1.239056699999999</v>
       </c>
       <c r="P50">
-        <v>4.849841599999997</v>
+        <v>4.661213299999995</v>
       </c>
       <c r="Q50">
-        <v>20.2498416</v>
+        <v>20.0612133</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1151907079020997</v>
+        <v>0.116386076753773</v>
       </c>
       <c r="T50">
-        <v>1.170027023419829</v>
+        <v>1.190182659551765</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.535647973642696</v>
+        <v>1.504308219078559</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09419589914442425</v>
+        <v>0.1186885039194275</v>
       </c>
       <c r="C51">
-        <v>94.26904729412496</v>
+        <v>20.79786165727555</v>
       </c>
       <c r="D51">
-        <v>215.196047294125</v>
+        <v>144.3778616572756</v>
       </c>
       <c r="E51">
-        <v>41.69700000000002</v>
+        <v>44.35000000000001</v>
       </c>
       <c r="F51">
-        <v>129.997</v>
+        <v>132.65</v>
       </c>
       <c r="G51">
         <v>9.07</v>
@@ -5469,45 +5469,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M51">
-        <v>11.69973</v>
+        <v>19.47302</v>
       </c>
       <c r="N51">
-        <v>5.900269999999994</v>
+        <v>-1.873020000000007</v>
       </c>
       <c r="O51">
-        <v>1.239056699999999</v>
+        <v>-0.3933342000000016</v>
       </c>
       <c r="P51">
-        <v>4.661213299999995</v>
+        <v>-1.479685800000006</v>
       </c>
       <c r="Q51">
-        <v>20.0612133</v>
+        <v>13.92031419999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.116386076753773</v>
+        <v>0.118439804672628</v>
       </c>
       <c r="T51">
-        <v>1.190182659551765</v>
+        <v>1.224811462693566</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.21</v>
+        <v>0.1898010683499528</v>
       </c>
       <c r="W51">
-        <v>0.0711</v>
+        <v>0.1189372031662269</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.504308219078559</v>
+        <v>0.9038146111902515</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1186885039194275</v>
+        <v>0.1196985039194275</v>
       </c>
       <c r="C52">
-        <v>20.79786165727555</v>
+        <v>16.21180966826691</v>
       </c>
       <c r="D52">
-        <v>144.3778616572756</v>
+        <v>142.4448096682669</v>
       </c>
       <c r="E52">
-        <v>44.35000000000001</v>
+        <v>47.003</v>
       </c>
       <c r="F52">
-        <v>132.65</v>
+        <v>135.303</v>
       </c>
       <c r="G52">
         <v>9.07</v>
@@ -5551,37 +5551,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M52">
-        <v>19.47302</v>
+        <v>19.8624804</v>
       </c>
       <c r="N52">
-        <v>-1.873020000000007</v>
+        <v>-2.262480400000008</v>
       </c>
       <c r="O52">
-        <v>-0.3933342000000016</v>
+        <v>-0.4751208840000017</v>
       </c>
       <c r="P52">
-        <v>-1.479685800000006</v>
+        <v>-1.787359516000007</v>
       </c>
       <c r="Q52">
-        <v>13.92031419999999</v>
+        <v>13.61264048399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.118439804672628</v>
+        <v>0.119922249665947</v>
       </c>
       <c r="T52">
-        <v>1.224811462693566</v>
+        <v>1.249807614993435</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1898010683499528</v>
+        <v>0.1860794787744635</v>
       </c>
       <c r="W52">
-        <v>0.1189372031662269</v>
+        <v>0.1194835325159088</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9038146111902515</v>
+        <v>0.8860927560688741</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1196985039194275</v>
+        <v>0.1207085039194275</v>
       </c>
       <c r="C53">
-        <v>16.21180966826691</v>
+        <v>11.67683643885437</v>
       </c>
       <c r="D53">
-        <v>142.4448096682669</v>
+        <v>140.5628364388544</v>
       </c>
       <c r="E53">
-        <v>47.003</v>
+        <v>49.65600000000002</v>
       </c>
       <c r="F53">
-        <v>135.303</v>
+        <v>137.956</v>
       </c>
       <c r="G53">
         <v>9.07</v>
@@ -5633,37 +5633,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M53">
-        <v>19.8624804</v>
+        <v>20.2519408</v>
       </c>
       <c r="N53">
-        <v>-2.262480400000008</v>
+        <v>-2.651940800000009</v>
       </c>
       <c r="O53">
-        <v>-0.4751208840000017</v>
+        <v>-0.5569075680000019</v>
       </c>
       <c r="P53">
-        <v>-1.787359516000007</v>
+        <v>-2.095033232000007</v>
       </c>
       <c r="Q53">
-        <v>13.61264048399999</v>
+        <v>13.30496676799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.119922249665947</v>
+        <v>0.1214664632006542</v>
       </c>
       <c r="T53">
-        <v>1.249807614993435</v>
+        <v>1.275845273639132</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1860794787744635</v>
+        <v>0.18250102725957</v>
       </c>
       <c r="W53">
-        <v>0.1194835325159088</v>
+        <v>0.1200088491982951</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8860927560688741</v>
+        <v>0.8690525107598572</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1207085039194275</v>
+        <v>0.1217185039194275</v>
       </c>
       <c r="C54">
-        <v>11.67683643885437</v>
+        <v>7.19094381894638</v>
       </c>
       <c r="D54">
-        <v>140.5628364388544</v>
+        <v>138.7299438189464</v>
       </c>
       <c r="E54">
-        <v>49.65600000000002</v>
+        <v>52.30900000000001</v>
       </c>
       <c r="F54">
-        <v>137.956</v>
+        <v>140.609</v>
       </c>
       <c r="G54">
         <v>9.07</v>
@@ -5715,37 +5715,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M54">
-        <v>20.2519408</v>
+        <v>20.6414012</v>
       </c>
       <c r="N54">
-        <v>-2.651940800000009</v>
+        <v>-3.04140120000001</v>
       </c>
       <c r="O54">
-        <v>-0.5569075680000019</v>
+        <v>-0.6386942520000021</v>
       </c>
       <c r="P54">
-        <v>-2.095033232000007</v>
+        <v>-2.402706948000008</v>
       </c>
       <c r="Q54">
-        <v>13.30496676799999</v>
+        <v>12.99729305199999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1214664632006542</v>
+        <v>0.1230763879496043</v>
       </c>
       <c r="T54">
-        <v>1.275845273639132</v>
+        <v>1.302990917759114</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.18250102725957</v>
+        <v>0.1790576116508989</v>
       </c>
       <c r="W54">
-        <v>0.1200088491982951</v>
+        <v>0.1205143426096481</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8690525107598572</v>
+        <v>0.8526552935757089</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1217185039194275</v>
+        <v>0.1227285039194275</v>
       </c>
       <c r="C55">
-        <v>7.19094381894638</v>
+        <v>2.752236537788662</v>
       </c>
       <c r="D55">
-        <v>138.7299438189464</v>
+        <v>136.9442365377887</v>
       </c>
       <c r="E55">
-        <v>52.30900000000001</v>
+        <v>54.96200000000003</v>
       </c>
       <c r="F55">
-        <v>140.609</v>
+        <v>143.262</v>
       </c>
       <c r="G55">
         <v>9.07</v>
@@ -5797,37 +5797,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M55">
-        <v>20.6414012</v>
+        <v>21.03086160000001</v>
       </c>
       <c r="N55">
-        <v>-3.04140120000001</v>
+        <v>-3.430861600000011</v>
       </c>
       <c r="O55">
-        <v>-0.6386942520000021</v>
+        <v>-0.7204809360000022</v>
       </c>
       <c r="P55">
-        <v>-2.402706948000008</v>
+        <v>-2.710380664000009</v>
       </c>
       <c r="Q55">
-        <v>12.99729305199999</v>
+        <v>12.68961933599999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1230763879496043</v>
+        <v>0.1247563094267696</v>
       </c>
       <c r="T55">
-        <v>1.302990917759114</v>
+        <v>1.331316807275616</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1790576116508989</v>
+        <v>0.17574172995366</v>
       </c>
       <c r="W55">
-        <v>0.1205143426096481</v>
+        <v>0.1210011140428027</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8526552935757089</v>
+        <v>0.8368653807317143</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1227285039194275</v>
+        <v>0.1237385039194275</v>
       </c>
       <c r="C56">
-        <v>2.752236537788662</v>
+        <v>-1.641084333114975</v>
       </c>
       <c r="D56">
-        <v>136.9442365377887</v>
+        <v>135.2039156668851</v>
       </c>
       <c r="E56">
-        <v>54.96200000000003</v>
+        <v>57.61500000000002</v>
       </c>
       <c r="F56">
-        <v>143.262</v>
+        <v>145.915</v>
       </c>
       <c r="G56">
         <v>9.07</v>
@@ -5879,37 +5879,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M56">
-        <v>21.03086160000001</v>
+        <v>21.42032200000001</v>
       </c>
       <c r="N56">
-        <v>-3.430861600000011</v>
+        <v>-3.820322000000012</v>
       </c>
       <c r="O56">
-        <v>-0.7204809360000022</v>
+        <v>-0.8022676200000024</v>
       </c>
       <c r="P56">
-        <v>-2.710380664000009</v>
+        <v>-3.018054380000009</v>
       </c>
       <c r="Q56">
-        <v>12.68961933599999</v>
+        <v>12.38194561999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1247563094267696</v>
+        <v>0.1265108940806978</v>
       </c>
       <c r="T56">
-        <v>1.331316807275616</v>
+        <v>1.360901625215074</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.17574172995366</v>
+        <v>0.1725464257726844</v>
       </c>
       <c r="W56">
-        <v>0.1210011140428027</v>
+        <v>0.1214701846965699</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8368653807317143</v>
+        <v>0.8216496465365922</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1237385039194275</v>
+        <v>0.1247485039194275</v>
       </c>
       <c r="C57">
-        <v>-1.641084333114975</v>
+        <v>-5.990727424887297</v>
       </c>
       <c r="D57">
-        <v>135.2039156668851</v>
+        <v>133.5072725751127</v>
       </c>
       <c r="E57">
-        <v>57.61500000000002</v>
+        <v>60.26800000000001</v>
       </c>
       <c r="F57">
-        <v>145.915</v>
+        <v>148.568</v>
       </c>
       <c r="G57">
         <v>9.07</v>
@@ -5961,37 +5961,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M57">
-        <v>21.42032200000001</v>
+        <v>21.8097824</v>
       </c>
       <c r="N57">
-        <v>-3.820322000000012</v>
+        <v>-4.209782400000009</v>
       </c>
       <c r="O57">
-        <v>-0.8022676200000024</v>
+        <v>-0.8840543040000018</v>
       </c>
       <c r="P57">
-        <v>-3.018054380000009</v>
+        <v>-3.325728096000007</v>
       </c>
       <c r="Q57">
-        <v>12.38194561999999</v>
+        <v>12.07427190399999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1265108940806978</v>
+        <v>0.1283452325825318</v>
       </c>
       <c r="T57">
-        <v>1.360901625215074</v>
+        <v>1.391831207606326</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1725464257726844</v>
+        <v>0.1694652395981721</v>
       </c>
       <c r="W57">
-        <v>0.1214701846965699</v>
+        <v>0.1219225028269883</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8216496465365922</v>
+        <v>0.8069773314198674</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1247485039194275</v>
+        <v>0.157562615015784</v>
       </c>
       <c r="C58">
-        <v>-5.990727424887297</v>
+        <v>-47.31027261744916</v>
       </c>
       <c r="D58">
-        <v>133.5072725751127</v>
+        <v>94.84072738255087</v>
       </c>
       <c r="E58">
-        <v>60.26800000000001</v>
+        <v>62.92100000000003</v>
       </c>
       <c r="F58">
-        <v>148.568</v>
+        <v>151.221</v>
       </c>
       <c r="G58">
         <v>9.07</v>
@@ -6043,45 +6043,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M58">
-        <v>21.8097824</v>
+        <v>30.36517680000001</v>
       </c>
       <c r="N58">
-        <v>-4.209782400000009</v>
+        <v>-12.76517680000001</v>
       </c>
       <c r="O58">
-        <v>-0.8840543040000018</v>
+        <v>-2.680687128000003</v>
       </c>
       <c r="P58">
-        <v>-3.325728096000007</v>
+        <v>-10.08448967200001</v>
       </c>
       <c r="Q58">
-        <v>12.07427190399999</v>
+        <v>5.31551032799999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1283452325825318</v>
+        <v>0.1326465428666756</v>
       </c>
       <c r="T58">
-        <v>1.391831207606326</v>
+        <v>1.464357478352291</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1694652395981721</v>
+        <v>0.1217183757678631</v>
       </c>
       <c r="W58">
-        <v>0.1219225028269883</v>
+        <v>0.1763589501458131</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8069773314198674</v>
+        <v>0.5796113131803003</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.157562615015784</v>
+        <v>0.159112615015784</v>
       </c>
       <c r="C59">
-        <v>-47.31027261744916</v>
+        <v>-51.24322935501161</v>
       </c>
       <c r="D59">
-        <v>94.84072738255087</v>
+        <v>93.56077064498842</v>
       </c>
       <c r="E59">
-        <v>62.92100000000003</v>
+        <v>65.57400000000003</v>
       </c>
       <c r="F59">
-        <v>151.221</v>
+        <v>153.874</v>
       </c>
       <c r="G59">
         <v>9.07</v>
@@ -6125,37 +6125,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M59">
-        <v>30.36517680000001</v>
+        <v>30.8978992</v>
       </c>
       <c r="N59">
-        <v>-12.76517680000001</v>
+        <v>-13.29789920000001</v>
       </c>
       <c r="O59">
-        <v>-2.680687128000003</v>
+        <v>-2.792558832000002</v>
       </c>
       <c r="P59">
-        <v>-10.08448967200001</v>
+        <v>-10.50534036800001</v>
       </c>
       <c r="Q59">
-        <v>5.31551032799999</v>
+        <v>4.894659631999991</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1326465428666756</v>
+        <v>0.1347143176968346</v>
       </c>
       <c r="T59">
-        <v>1.464357478352291</v>
+        <v>1.499223132598773</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1217183757678631</v>
+        <v>0.1196197830822103</v>
       </c>
       <c r="W59">
-        <v>0.1763589501458131</v>
+        <v>0.1767803475570922</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5796113131803003</v>
+        <v>0.5696180146771918</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1591126150157839</v>
+        <v>0.160662615015784</v>
       </c>
       <c r="C60">
-        <v>-51.24322935501155</v>
+        <v>-55.14209791966871</v>
       </c>
       <c r="D60">
-        <v>93.56077064498845</v>
+        <v>92.31490208033127</v>
       </c>
       <c r="E60">
-        <v>65.574</v>
+        <v>68.22699999999999</v>
       </c>
       <c r="F60">
-        <v>153.874</v>
+        <v>156.527</v>
       </c>
       <c r="G60">
         <v>9.07</v>
@@ -6207,37 +6207,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M60">
-        <v>30.8978992</v>
+        <v>31.4306216</v>
       </c>
       <c r="N60">
-        <v>-13.29789920000001</v>
+        <v>-13.8306216</v>
       </c>
       <c r="O60">
-        <v>-2.792558832000001</v>
+        <v>-2.904430536000001</v>
       </c>
       <c r="P60">
-        <v>-10.50534036800001</v>
+        <v>-10.926191064</v>
       </c>
       <c r="Q60">
-        <v>4.894659631999994</v>
+        <v>4.473808935999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1347143176968345</v>
+        <v>0.1368829595918793</v>
       </c>
       <c r="T60">
-        <v>1.499223132598773</v>
+        <v>1.535789550467036</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1196197830822103</v>
+        <v>0.1175923291316643</v>
       </c>
       <c r="W60">
-        <v>0.1767803475570922</v>
+        <v>0.1771874603103618</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5696180146771919</v>
+        <v>0.5599634720555445</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.160662615015784</v>
+        <v>0.162212615015784</v>
       </c>
       <c r="C61">
-        <v>-55.14209791966871</v>
+        <v>-59.00822218512192</v>
       </c>
       <c r="D61">
-        <v>92.31490208033127</v>
+        <v>91.10177781487808</v>
       </c>
       <c r="E61">
-        <v>68.22699999999999</v>
+        <v>70.88000000000001</v>
       </c>
       <c r="F61">
-        <v>156.527</v>
+        <v>159.18</v>
       </c>
       <c r="G61">
         <v>9.07</v>
@@ -6289,37 +6289,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M61">
-        <v>31.4306216</v>
+        <v>31.963344</v>
       </c>
       <c r="N61">
-        <v>-13.8306216</v>
+        <v>-14.36334400000001</v>
       </c>
       <c r="O61">
-        <v>-2.904430536000001</v>
+        <v>-3.016302240000002</v>
       </c>
       <c r="P61">
-        <v>-10.926191064</v>
+        <v>-11.34704176000001</v>
       </c>
       <c r="Q61">
-        <v>4.473808935999998</v>
+        <v>4.052958239999993</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1368829595918793</v>
+        <v>0.1391600335816763</v>
       </c>
       <c r="T61">
-        <v>1.535789550467036</v>
+        <v>1.574184289228712</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1175923291316643</v>
+        <v>0.1156324569794699</v>
       </c>
       <c r="W61">
-        <v>0.1771874603103618</v>
+        <v>0.1775810026385224</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5599634720555445</v>
+        <v>0.5506307475212854</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.162212615015784</v>
+        <v>0.163762615015784</v>
       </c>
       <c r="C62">
-        <v>-59.00822218512192</v>
+        <v>-62.84287630112522</v>
       </c>
       <c r="D62">
-        <v>91.10177781487808</v>
+        <v>89.92012369887479</v>
       </c>
       <c r="E62">
-        <v>70.88000000000001</v>
+        <v>73.533</v>
       </c>
       <c r="F62">
-        <v>159.18</v>
+        <v>161.833</v>
       </c>
       <c r="G62">
         <v>9.07</v>
@@ -6371,37 +6371,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M62">
-        <v>31.963344</v>
+        <v>32.4960664</v>
       </c>
       <c r="N62">
-        <v>-14.36334400000001</v>
+        <v>-14.89606640000001</v>
       </c>
       <c r="O62">
-        <v>-3.016302240000002</v>
+        <v>-3.128173944000002</v>
       </c>
       <c r="P62">
-        <v>-11.34704176000001</v>
+        <v>-11.76789245600001</v>
       </c>
       <c r="Q62">
-        <v>4.052958239999993</v>
+        <v>3.632107543999993</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1391600335816763</v>
+        <v>0.141553880596591</v>
       </c>
       <c r="T62">
-        <v>1.574184289228712</v>
+        <v>1.614547988952525</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1156324569794699</v>
+        <v>0.1137368429306262</v>
       </c>
       <c r="W62">
-        <v>0.1775810026385224</v>
+        <v>0.1779616419395303</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5506307475212854</v>
+        <v>0.5416040139553626</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.163762615015784</v>
+        <v>0.165312615015784</v>
       </c>
       <c r="C63">
-        <v>-62.84287630112522</v>
+        <v>-66.64726915742773</v>
       </c>
       <c r="D63">
-        <v>89.92012369887479</v>
+        <v>88.7687308425723</v>
       </c>
       <c r="E63">
-        <v>73.533</v>
+        <v>76.18600000000002</v>
       </c>
       <c r="F63">
-        <v>161.833</v>
+        <v>164.486</v>
       </c>
       <c r="G63">
         <v>9.07</v>
@@ -6453,37 +6453,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M63">
-        <v>32.4960664</v>
+        <v>33.02878880000001</v>
       </c>
       <c r="N63">
-        <v>-14.89606640000001</v>
+        <v>-15.42878880000001</v>
       </c>
       <c r="O63">
-        <v>-3.128173944000002</v>
+        <v>-3.240045648000003</v>
       </c>
       <c r="P63">
-        <v>-11.76789245600001</v>
+        <v>-12.18874315200001</v>
       </c>
       <c r="Q63">
-        <v>3.632107543999993</v>
+        <v>3.211256847999989</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.141553880596591</v>
+        <v>0.1440737195596592</v>
       </c>
       <c r="T63">
-        <v>1.614547988952525</v>
+        <v>1.65703609392496</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1137368429306262</v>
+        <v>0.1119023777220677</v>
       </c>
       <c r="W63">
-        <v>0.1779616419395303</v>
+        <v>0.1783300025534088</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5416040139553626</v>
+        <v>0.5328684653431793</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.165312615015784</v>
+        <v>0.166862615015784</v>
       </c>
       <c r="C64">
-        <v>-66.64726915742773</v>
+        <v>-70.42254850909805</v>
       </c>
       <c r="D64">
-        <v>88.7687308425723</v>
+        <v>87.64645149090195</v>
       </c>
       <c r="E64">
-        <v>76.18600000000002</v>
+        <v>78.83900000000001</v>
       </c>
       <c r="F64">
-        <v>164.486</v>
+        <v>167.139</v>
       </c>
       <c r="G64">
         <v>9.07</v>
@@ -6535,37 +6535,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M64">
-        <v>33.02878880000001</v>
+        <v>33.56151120000001</v>
       </c>
       <c r="N64">
-        <v>-15.42878880000001</v>
+        <v>-15.96151120000001</v>
       </c>
       <c r="O64">
-        <v>-3.240045648000003</v>
+        <v>-3.351917352000002</v>
       </c>
       <c r="P64">
-        <v>-12.18874315200001</v>
+        <v>-12.60959384800001</v>
       </c>
       <c r="Q64">
-        <v>3.211256847999989</v>
+        <v>2.790406151999992</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1440737195596592</v>
+        <v>0.1467297660342446</v>
       </c>
       <c r="T64">
-        <v>1.65703609392496</v>
+        <v>1.701820853220229</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1119023777220677</v>
+        <v>0.1101261495042571</v>
       </c>
       <c r="W64">
-        <v>0.1783300025534088</v>
+        <v>0.1786866691795452</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5328684653431793</v>
+        <v>0.5244102357345575</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.166862615015784</v>
+        <v>0.168412615015784</v>
       </c>
       <c r="C65">
-        <v>-70.42254850909805</v>
+        <v>-74.16980479282276</v>
       </c>
       <c r="D65">
-        <v>87.64645149090195</v>
+        <v>86.55219520717725</v>
       </c>
       <c r="E65">
-        <v>78.83900000000001</v>
+        <v>81.492</v>
       </c>
       <c r="F65">
-        <v>167.139</v>
+        <v>169.792</v>
       </c>
       <c r="G65">
         <v>9.07</v>
@@ -6617,37 +6617,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M65">
-        <v>33.56151120000001</v>
+        <v>34.0942336</v>
       </c>
       <c r="N65">
-        <v>-15.96151120000001</v>
+        <v>-16.49423360000001</v>
       </c>
       <c r="O65">
-        <v>-3.351917352000002</v>
+        <v>-3.463789056000002</v>
       </c>
       <c r="P65">
-        <v>-12.60959384800001</v>
+        <v>-13.03044454400001</v>
       </c>
       <c r="Q65">
-        <v>2.790406151999992</v>
+        <v>2.369555455999993</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1467297660342446</v>
+        <v>0.149533370646307</v>
       </c>
       <c r="T65">
-        <v>1.701820853220229</v>
+        <v>1.749093654698569</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1101261495042571</v>
+        <v>0.1084054284182531</v>
       </c>
       <c r="W65">
-        <v>0.1786866691795452</v>
+        <v>0.1790321899736148</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5244102357345575</v>
+        <v>0.5162163258012051</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.168412615015784</v>
+        <v>0.169962615015784</v>
       </c>
       <c r="C66">
-        <v>-74.16980479282276</v>
+        <v>-77.89007466085403</v>
       </c>
       <c r="D66">
-        <v>86.55219520717725</v>
+        <v>85.484925339146</v>
       </c>
       <c r="E66">
-        <v>81.492</v>
+        <v>84.14500000000002</v>
       </c>
       <c r="F66">
-        <v>169.792</v>
+        <v>172.445</v>
       </c>
       <c r="G66">
         <v>9.07</v>
@@ -6699,37 +6699,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M66">
-        <v>34.0942336</v>
+        <v>34.62695600000001</v>
       </c>
       <c r="N66">
-        <v>-16.49423360000001</v>
+        <v>-17.02695600000001</v>
       </c>
       <c r="O66">
-        <v>-3.463789056000002</v>
+        <v>-3.575660760000003</v>
       </c>
       <c r="P66">
-        <v>-13.03044454400001</v>
+        <v>-13.45129524000001</v>
       </c>
       <c r="Q66">
-        <v>2.369555455999993</v>
+        <v>1.948704759999989</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.149533370646307</v>
+        <v>0.1524971812362015</v>
       </c>
       <c r="T66">
-        <v>1.749093654698569</v>
+        <v>1.799067759118528</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1084054284182531</v>
+        <v>0.1067376525964338</v>
       </c>
       <c r="W66">
-        <v>0.1790321899736148</v>
+        <v>0.1793670793586361</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5162163258012051</v>
+        <v>0.5082745361734942</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.169962615015784</v>
+        <v>0.171512615015784</v>
       </c>
       <c r="C67">
-        <v>-77.89007466085403</v>
+        <v>-81.5843442566802</v>
       </c>
       <c r="D67">
-        <v>85.484925339146</v>
+        <v>84.44365574331981</v>
       </c>
       <c r="E67">
-        <v>84.14500000000002</v>
+        <v>86.79800000000002</v>
       </c>
       <c r="F67">
-        <v>172.445</v>
+        <v>175.098</v>
       </c>
       <c r="G67">
         <v>9.07</v>
@@ -6781,37 +6781,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M67">
-        <v>34.62695600000001</v>
+        <v>35.1596784</v>
       </c>
       <c r="N67">
-        <v>-17.02695600000001</v>
+        <v>-17.55967840000001</v>
       </c>
       <c r="O67">
-        <v>-3.575660760000003</v>
+        <v>-3.687532464000002</v>
       </c>
       <c r="P67">
-        <v>-13.45129524000001</v>
+        <v>-13.87214593600001</v>
       </c>
       <c r="Q67">
-        <v>1.948704759999989</v>
+        <v>1.527854063999992</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1524971812362015</v>
+        <v>0.1556353336255015</v>
       </c>
       <c r="T67">
-        <v>1.799067759118528</v>
+        <v>1.851981516739661</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1067376525964338</v>
+        <v>0.1051204154358817</v>
       </c>
       <c r="W67">
-        <v>0.1793670793586361</v>
+        <v>0.1796918205804749</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5082745361734942</v>
+        <v>0.5005734068375322</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.171512615015784</v>
+        <v>0.1969258562130541</v>
       </c>
       <c r="C68">
-        <v>-81.5843442566802</v>
+        <v>-98.29433609291797</v>
       </c>
       <c r="D68">
-        <v>84.44365574331981</v>
+        <v>70.38666390708202</v>
       </c>
       <c r="E68">
-        <v>86.79800000000002</v>
+        <v>89.45100000000001</v>
       </c>
       <c r="F68">
-        <v>175.098</v>
+        <v>177.751</v>
       </c>
       <c r="G68">
         <v>9.07</v>
@@ -6863,45 +6863,45 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M68">
-        <v>35.1596784</v>
+        <v>41.9136858</v>
       </c>
       <c r="N68">
-        <v>-17.55967840000001</v>
+        <v>-24.31368580000001</v>
       </c>
       <c r="O68">
-        <v>-3.687532464000002</v>
+        <v>-5.105874018000002</v>
       </c>
       <c r="P68">
-        <v>-13.87214593600001</v>
+        <v>-19.20781178200001</v>
       </c>
       <c r="Q68">
-        <v>1.527854063999992</v>
+        <v>-3.807811782000007</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1556353336255015</v>
+        <v>0.1602159231210322</v>
       </c>
       <c r="T68">
-        <v>1.851981516739661</v>
+        <v>1.929216836208159</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1051204154358817</v>
+        <v>0.08818122122774509</v>
       </c>
       <c r="W68">
-        <v>0.1796918205804749</v>
+        <v>0.2150068680344977</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5005734068375322</v>
+        <v>0.4199105772749767</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1969258562130541</v>
+        <v>0.1988258562130541</v>
       </c>
       <c r="C69">
-        <v>-98.29433609291797</v>
+        <v>-101.8125780184992</v>
       </c>
       <c r="D69">
-        <v>70.38666390708202</v>
+        <v>69.52142198150079</v>
       </c>
       <c r="E69">
-        <v>89.45100000000001</v>
+        <v>92.10400000000003</v>
       </c>
       <c r="F69">
-        <v>177.751</v>
+        <v>180.404</v>
       </c>
       <c r="G69">
         <v>9.07</v>
@@ -6945,37 +6945,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M69">
-        <v>41.9136858</v>
+        <v>42.53926320000001</v>
       </c>
       <c r="N69">
-        <v>-24.31368580000001</v>
+        <v>-24.93926320000001</v>
       </c>
       <c r="O69">
-        <v>-5.105874018000002</v>
+        <v>-5.237245272000003</v>
       </c>
       <c r="P69">
-        <v>-19.20781178200001</v>
+        <v>-19.70201792800001</v>
       </c>
       <c r="Q69">
-        <v>-3.807811782000007</v>
+        <v>-4.30201792800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1602159231210322</v>
+        <v>0.1637914207185644</v>
       </c>
       <c r="T69">
-        <v>1.929216836208159</v>
+        <v>1.989504862339664</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08818122122774509</v>
+        <v>0.08688443856263119</v>
       </c>
       <c r="W69">
-        <v>0.2150068680344977</v>
+        <v>0.2153126493869316</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4199105772749767</v>
+        <v>0.4137354217268152</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1988258562130541</v>
+        <v>0.2007258562130541</v>
       </c>
       <c r="C70">
-        <v>-101.8125780184992</v>
+        <v>-105.3098059492677</v>
       </c>
       <c r="D70">
-        <v>69.52142198150079</v>
+        <v>68.67719405073234</v>
       </c>
       <c r="E70">
-        <v>92.10400000000003</v>
+        <v>94.75700000000002</v>
       </c>
       <c r="F70">
-        <v>180.404</v>
+        <v>183.057</v>
       </c>
       <c r="G70">
         <v>9.07</v>
@@ -7027,37 +7027,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M70">
-        <v>42.53926320000001</v>
+        <v>43.16484060000001</v>
       </c>
       <c r="N70">
-        <v>-24.93926320000001</v>
+        <v>-25.56484060000001</v>
       </c>
       <c r="O70">
-        <v>-5.237245272000003</v>
+        <v>-5.368616526000002</v>
       </c>
       <c r="P70">
-        <v>-19.70201792800001</v>
+        <v>-20.19622407400001</v>
       </c>
       <c r="Q70">
-        <v>-4.30201792800001</v>
+        <v>-4.796224074000007</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1637914207185644</v>
+        <v>0.1675975955804536</v>
       </c>
       <c r="T70">
-        <v>1.989504862339664</v>
+        <v>2.05368243854417</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08688443856263119</v>
+        <v>0.08562524380085393</v>
       </c>
       <c r="W70">
-        <v>0.2153126493869316</v>
+        <v>0.2156095675117587</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4137354217268152</v>
+        <v>0.4077392561945425</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2007258562130541</v>
+        <v>0.2026258562130541</v>
       </c>
       <c r="C71">
-        <v>-105.3098059492677</v>
+        <v>-108.7867762458075</v>
       </c>
       <c r="D71">
-        <v>68.67719405073234</v>
+        <v>67.8532237541925</v>
       </c>
       <c r="E71">
-        <v>94.75700000000002</v>
+        <v>97.41000000000004</v>
       </c>
       <c r="F71">
-        <v>183.057</v>
+        <v>185.71</v>
       </c>
       <c r="G71">
         <v>9.07</v>
@@ -7109,37 +7109,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M71">
-        <v>43.16484060000001</v>
+        <v>43.79041800000001</v>
       </c>
       <c r="N71">
-        <v>-25.56484060000001</v>
+        <v>-26.19041800000002</v>
       </c>
       <c r="O71">
-        <v>-5.368616526000002</v>
+        <v>-5.499987780000003</v>
       </c>
       <c r="P71">
-        <v>-20.19622407400001</v>
+        <v>-20.69043022000001</v>
       </c>
       <c r="Q71">
-        <v>-4.796224074000007</v>
+        <v>-5.29043022000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1675975955804536</v>
+        <v>0.1716575154331354</v>
       </c>
       <c r="T71">
-        <v>2.05368243854417</v>
+        <v>2.122138519828975</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08562524380085393</v>
+        <v>0.08440202603227029</v>
       </c>
       <c r="W71">
-        <v>0.2156095675117587</v>
+        <v>0.2158980022615907</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4077392561945425</v>
+        <v>0.4019144096774776</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2026258562130541</v>
+        <v>0.2045258562130541</v>
       </c>
       <c r="C72">
-        <v>-108.7867762458075</v>
+        <v>-112.2442094006043</v>
       </c>
       <c r="D72">
-        <v>67.8532237541925</v>
+        <v>67.04879059939567</v>
       </c>
       <c r="E72">
-        <v>97.41000000000004</v>
+        <v>100.063</v>
       </c>
       <c r="F72">
-        <v>185.71</v>
+        <v>188.363</v>
       </c>
       <c r="G72">
         <v>9.07</v>
@@ -7191,37 +7191,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M72">
-        <v>43.79041800000001</v>
+        <v>44.41599540000001</v>
       </c>
       <c r="N72">
-        <v>-26.19041800000002</v>
+        <v>-26.81599540000001</v>
       </c>
       <c r="O72">
-        <v>-5.499987780000003</v>
+        <v>-5.631359034000003</v>
       </c>
       <c r="P72">
-        <v>-20.69043022000001</v>
+        <v>-21.18463636600001</v>
       </c>
       <c r="Q72">
-        <v>-5.29043022000001</v>
+        <v>-5.78463636600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1716575154331354</v>
+        <v>0.1759974297584159</v>
       </c>
       <c r="T72">
-        <v>2.122138519828975</v>
+        <v>2.195315710167905</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08440202603227029</v>
+        <v>0.08321326510223832</v>
       </c>
       <c r="W72">
-        <v>0.2158980022615907</v>
+        <v>0.2161783120888922</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4019144096774776</v>
+        <v>0.396253643343992</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2045258562130541</v>
+        <v>0.2064258562130541</v>
       </c>
       <c r="C73">
-        <v>-112.2442094006043</v>
+        <v>-115.6827921393028</v>
       </c>
       <c r="D73">
-        <v>67.04879059939567</v>
+        <v>66.26320786069721</v>
       </c>
       <c r="E73">
-        <v>100.063</v>
+        <v>102.716</v>
       </c>
       <c r="F73">
-        <v>188.363</v>
+        <v>191.016</v>
       </c>
       <c r="G73">
         <v>9.07</v>
@@ -7273,37 +7273,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M73">
-        <v>44.4159954</v>
+        <v>45.0415728</v>
       </c>
       <c r="N73">
-        <v>-26.81599540000001</v>
+        <v>-27.4415728</v>
       </c>
       <c r="O73">
-        <v>-5.631359034000001</v>
+        <v>-5.762730288</v>
       </c>
       <c r="P73">
-        <v>-21.18463636600001</v>
+        <v>-21.678842512</v>
       </c>
       <c r="Q73">
-        <v>-5.784636366000006</v>
+        <v>-6.278842512000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1759974297584159</v>
+        <v>0.1806473379640736</v>
       </c>
       <c r="T73">
-        <v>2.195315710167905</v>
+        <v>2.273719842673902</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08321326510223834</v>
+        <v>0.08205752530915171</v>
       </c>
       <c r="W73">
-        <v>0.2161783120888922</v>
+        <v>0.216450835532102</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3962536433439922</v>
+        <v>0.39075012051977</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2064258562130541</v>
+        <v>0.2083258562130541</v>
       </c>
       <c r="C74">
-        <v>-115.6827921393028</v>
+        <v>-119.1031793759579</v>
       </c>
       <c r="D74">
-        <v>66.26320786069721</v>
+        <v>65.49582062404208</v>
       </c>
       <c r="E74">
-        <v>102.716</v>
+        <v>105.369</v>
       </c>
       <c r="F74">
-        <v>191.016</v>
+        <v>193.669</v>
       </c>
       <c r="G74">
         <v>9.07</v>
@@ -7355,37 +7355,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M74">
-        <v>45.0415728</v>
+        <v>45.6671502</v>
       </c>
       <c r="N74">
-        <v>-27.4415728</v>
+        <v>-28.06715020000001</v>
       </c>
       <c r="O74">
-        <v>-5.762730288</v>
+        <v>-5.894101542000001</v>
       </c>
       <c r="P74">
-        <v>-21.678842512</v>
+        <v>-22.17304865800001</v>
       </c>
       <c r="Q74">
-        <v>-6.278842512000002</v>
+        <v>-6.773048658000006</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1806473379640736</v>
+        <v>0.1856416838145948</v>
       </c>
       <c r="T74">
-        <v>2.273719842673902</v>
+        <v>2.35793168869886</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08205752530915171</v>
+        <v>0.08093344961998523</v>
       </c>
       <c r="W74">
-        <v>0.216450835532102</v>
+        <v>0.2167158925796075</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.39075012051977</v>
+        <v>0.3853973791427868</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2083258562130541</v>
+        <v>0.2102258562130541</v>
       </c>
       <c r="C75">
-        <v>-119.1031793759579</v>
+        <v>-122.5059960339802</v>
       </c>
       <c r="D75">
-        <v>65.49582062404208</v>
+        <v>64.74600396601977</v>
       </c>
       <c r="E75">
-        <v>105.369</v>
+        <v>108.022</v>
       </c>
       <c r="F75">
-        <v>193.669</v>
+        <v>196.322</v>
       </c>
       <c r="G75">
         <v>9.07</v>
@@ -7437,37 +7437,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M75">
-        <v>45.6671502</v>
+        <v>46.2927276</v>
       </c>
       <c r="N75">
-        <v>-28.06715020000001</v>
+        <v>-28.6927276</v>
       </c>
       <c r="O75">
-        <v>-5.894101542000001</v>
+        <v>-6.025472796000001</v>
       </c>
       <c r="P75">
-        <v>-22.17304865800001</v>
+        <v>-22.667254804</v>
       </c>
       <c r="Q75">
-        <v>-6.773048658000006</v>
+        <v>-7.267254804000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1856416838145948</v>
+        <v>0.1910202101151562</v>
       </c>
       <c r="T75">
-        <v>2.35793168869886</v>
+        <v>2.448621369033432</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08093344961998523</v>
+        <v>0.0798397543548503</v>
       </c>
       <c r="W75">
-        <v>0.2167158925796075</v>
+        <v>0.2169737859231263</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3853973791427868</v>
+        <v>0.3801893064516682</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2102258562130541</v>
+        <v>0.2121258562130541</v>
       </c>
       <c r="C76">
-        <v>-122.5059960339802</v>
+        <v>-125.8918387434162</v>
       </c>
       <c r="D76">
-        <v>64.74600396601977</v>
+        <v>64.01316125658384</v>
       </c>
       <c r="E76">
-        <v>108.022</v>
+        <v>110.675</v>
       </c>
       <c r="F76">
-        <v>196.322</v>
+        <v>198.975</v>
       </c>
       <c r="G76">
         <v>9.07</v>
@@ -7519,37 +7519,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M76">
-        <v>46.2927276</v>
+        <v>46.91830500000001</v>
       </c>
       <c r="N76">
-        <v>-28.6927276</v>
+        <v>-29.31830500000002</v>
       </c>
       <c r="O76">
-        <v>-6.025472796000001</v>
+        <v>-6.156844050000004</v>
       </c>
       <c r="P76">
-        <v>-22.667254804</v>
+        <v>-23.16146095000001</v>
       </c>
       <c r="Q76">
-        <v>-7.267254804000002</v>
+        <v>-7.761460950000012</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1910202101151562</v>
+        <v>0.1968290185197624</v>
       </c>
       <c r="T76">
-        <v>2.448621369033432</v>
+        <v>2.54656622379477</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0798397543548503</v>
+        <v>0.07877522429678561</v>
       </c>
       <c r="W76">
-        <v>0.2169737859231263</v>
+        <v>0.217224802110818</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3801893064516682</v>
+        <v>0.3751201156989791</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2121258562130541</v>
+        <v>0.2140258562130541</v>
       </c>
       <c r="C77">
-        <v>-125.8918387434162</v>
+        <v>-129.2612774242523</v>
       </c>
       <c r="D77">
-        <v>64.01316125658384</v>
+        <v>63.29672257574769</v>
       </c>
       <c r="E77">
-        <v>110.675</v>
+        <v>113.328</v>
       </c>
       <c r="F77">
-        <v>198.975</v>
+        <v>201.628</v>
       </c>
       <c r="G77">
         <v>9.07</v>
@@ -7601,37 +7601,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M77">
-        <v>46.91830500000001</v>
+        <v>47.54388240000001</v>
       </c>
       <c r="N77">
-        <v>-29.31830500000002</v>
+        <v>-29.94388240000001</v>
       </c>
       <c r="O77">
-        <v>-6.156844050000004</v>
+        <v>-6.288215304000003</v>
       </c>
       <c r="P77">
-        <v>-23.16146095000001</v>
+        <v>-23.65566709600001</v>
       </c>
       <c r="Q77">
-        <v>-7.761460950000012</v>
+        <v>-8.255667096000009</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1968290185197624</v>
+        <v>0.2031218942914192</v>
       </c>
       <c r="T77">
-        <v>2.54656622379477</v>
+        <v>2.652673149786219</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07877522429678561</v>
+        <v>0.07773870818761738</v>
       </c>
       <c r="W77">
-        <v>0.217224802110818</v>
+        <v>0.2174692126093598</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3751201156989791</v>
+        <v>0.3701843247029399</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2140258562130541</v>
+        <v>0.2159258562130541</v>
       </c>
       <c r="C78">
-        <v>-129.2612774242523</v>
+        <v>-132.6148567645736</v>
       </c>
       <c r="D78">
-        <v>63.29672257574769</v>
+        <v>62.59614323542637</v>
       </c>
       <c r="E78">
-        <v>113.328</v>
+        <v>115.981</v>
       </c>
       <c r="F78">
-        <v>201.628</v>
+        <v>204.281</v>
       </c>
       <c r="G78">
         <v>9.07</v>
@@ -7683,37 +7683,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M78">
-        <v>47.54388240000001</v>
+        <v>48.16945980000001</v>
       </c>
       <c r="N78">
-        <v>-29.94388240000001</v>
+        <v>-30.56945980000001</v>
       </c>
       <c r="O78">
-        <v>-6.288215304000003</v>
+        <v>-6.419586558000002</v>
       </c>
       <c r="P78">
-        <v>-23.65566709600001</v>
+        <v>-24.14987324200001</v>
       </c>
       <c r="Q78">
-        <v>-8.255667096000009</v>
+        <v>-8.749873242000008</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2031218942914192</v>
+        <v>0.2099619766519157</v>
       </c>
       <c r="T78">
-        <v>2.652673149786219</v>
+        <v>2.768006764994316</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07773870818761738</v>
+        <v>0.07672911457479119</v>
       </c>
       <c r="W78">
-        <v>0.2174692126093598</v>
+        <v>0.2177072747832643</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3701843247029399</v>
+        <v>0.3653767360704342</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2159258562130541</v>
+        <v>0.2178258562130541</v>
       </c>
       <c r="C79">
-        <v>-132.6148567645736</v>
+        <v>-135.9530976016334</v>
       </c>
       <c r="D79">
-        <v>62.59614323542637</v>
+        <v>61.91090239836658</v>
       </c>
       <c r="E79">
-        <v>115.981</v>
+        <v>118.634</v>
       </c>
       <c r="F79">
-        <v>204.281</v>
+        <v>206.934</v>
       </c>
       <c r="G79">
         <v>9.07</v>
@@ -7765,37 +7765,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M79">
-        <v>48.16945980000001</v>
+        <v>48.79503720000001</v>
       </c>
       <c r="N79">
-        <v>-30.56945980000001</v>
+        <v>-31.19503720000002</v>
       </c>
       <c r="O79">
-        <v>-6.419586558000002</v>
+        <v>-6.550957812000003</v>
       </c>
       <c r="P79">
-        <v>-24.14987324200001</v>
+        <v>-24.64407938800001</v>
       </c>
       <c r="Q79">
-        <v>-8.749873242000008</v>
+        <v>-9.244079388000012</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2099619766519157</v>
+        <v>0.2174238846815482</v>
       </c>
       <c r="T79">
-        <v>2.768006764994316</v>
+        <v>2.893825254312238</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07672911457479119</v>
+        <v>0.07574540797767848</v>
       </c>
       <c r="W79">
-        <v>0.2177072747832643</v>
+        <v>0.2179392327988634</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3653767360704342</v>
+        <v>0.3606924189413261</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2178258562130541</v>
+        <v>0.2197258562130541</v>
       </c>
       <c r="C80">
-        <v>-135.9530976016334</v>
+        <v>-139.2764982131938</v>
       </c>
       <c r="D80">
-        <v>61.91090239836658</v>
+        <v>61.24050178680623</v>
       </c>
       <c r="E80">
-        <v>118.634</v>
+        <v>121.287</v>
       </c>
       <c r="F80">
-        <v>206.934</v>
+        <v>209.587</v>
       </c>
       <c r="G80">
         <v>9.07</v>
@@ -7847,37 +7847,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M80">
-        <v>48.79503720000001</v>
+        <v>49.42061460000001</v>
       </c>
       <c r="N80">
-        <v>-31.19503720000002</v>
+        <v>-31.82061460000001</v>
       </c>
       <c r="O80">
-        <v>-6.550957812000003</v>
+        <v>-6.682329066000002</v>
       </c>
       <c r="P80">
-        <v>-24.64407938800001</v>
+        <v>-25.13828553400001</v>
       </c>
       <c r="Q80">
-        <v>-9.244079388000012</v>
+        <v>-9.738285534000012</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2174238846815482</v>
+        <v>0.2255964506187648</v>
       </c>
       <c r="T80">
-        <v>2.893825254312238</v>
+        <v>3.031626456898536</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07574540797767848</v>
+        <v>0.07478660534504963</v>
       </c>
       <c r="W80">
-        <v>0.2179392327988634</v>
+        <v>0.2181653184596373</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3606924189413261</v>
+        <v>0.356126692119284</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2197258562130541</v>
+        <v>0.2216258562130541</v>
       </c>
       <c r="C81">
-        <v>-139.2764982131938</v>
+        <v>-142.5855355258657</v>
       </c>
       <c r="D81">
-        <v>61.24050178680623</v>
+        <v>60.58446447413432</v>
       </c>
       <c r="E81">
-        <v>121.287</v>
+        <v>123.94</v>
       </c>
       <c r="F81">
-        <v>209.587</v>
+        <v>212.24</v>
       </c>
       <c r="G81">
         <v>9.07</v>
@@ -7929,37 +7929,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M81">
-        <v>49.42061460000001</v>
+        <v>50.046192</v>
       </c>
       <c r="N81">
-        <v>-31.82061460000001</v>
+        <v>-32.44619200000001</v>
       </c>
       <c r="O81">
-        <v>-6.682329066000002</v>
+        <v>-6.813700320000002</v>
       </c>
       <c r="P81">
-        <v>-25.13828553400001</v>
+        <v>-25.63249168000001</v>
       </c>
       <c r="Q81">
-        <v>-9.738285534000012</v>
+        <v>-10.23249168000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2255964506187648</v>
+        <v>0.2345862731497031</v>
       </c>
       <c r="T81">
-        <v>3.031626456898536</v>
+        <v>3.183207779743463</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07478660534504963</v>
+        <v>0.07385177277823653</v>
       </c>
       <c r="W81">
-        <v>0.2181653184596373</v>
+        <v>0.2183857519788918</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.356126692119284</v>
+        <v>0.3516751084677929</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2216258562130541</v>
+        <v>0.2235258562130541</v>
       </c>
       <c r="C82">
-        <v>-142.5855355258657</v>
+        <v>-145.880666246606</v>
       </c>
       <c r="D82">
-        <v>60.58446447413432</v>
+        <v>59.94233375339399</v>
       </c>
       <c r="E82">
-        <v>123.94</v>
+        <v>126.593</v>
       </c>
       <c r="F82">
-        <v>212.24</v>
+        <v>214.893</v>
       </c>
       <c r="G82">
         <v>9.07</v>
@@ -8011,37 +8011,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M82">
-        <v>50.046192</v>
+        <v>50.67176940000001</v>
       </c>
       <c r="N82">
-        <v>-32.44619200000001</v>
+        <v>-33.07176940000002</v>
       </c>
       <c r="O82">
-        <v>-6.813700320000002</v>
+        <v>-6.945071574000003</v>
       </c>
       <c r="P82">
-        <v>-25.63249168000001</v>
+        <v>-26.12669782600001</v>
       </c>
       <c r="Q82">
-        <v>-10.23249168000001</v>
+        <v>-10.72669782600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2345862731497031</v>
+        <v>0.2445223927891612</v>
       </c>
       <c r="T82">
-        <v>3.183207779743463</v>
+        <v>3.350745031308909</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07385177277823653</v>
+        <v>0.07294002249702371</v>
       </c>
       <c r="W82">
-        <v>0.2183857519788918</v>
+        <v>0.2186007426952018</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3516751084677929</v>
+        <v>0.3473334404620178</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2235258562130541</v>
+        <v>0.2254258562130541</v>
       </c>
       <c r="C83">
-        <v>-145.880666246606</v>
+        <v>-149.1623279230134</v>
       </c>
       <c r="D83">
-        <v>59.94233375339399</v>
+        <v>59.31367207698664</v>
       </c>
       <c r="E83">
-        <v>126.593</v>
+        <v>129.246</v>
       </c>
       <c r="F83">
-        <v>214.893</v>
+        <v>217.546</v>
       </c>
       <c r="G83">
         <v>9.07</v>
@@ -8093,37 +8093,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M83">
-        <v>50.67176940000001</v>
+        <v>51.29734680000001</v>
       </c>
       <c r="N83">
-        <v>-33.07176940000002</v>
+        <v>-33.69734680000001</v>
       </c>
       <c r="O83">
-        <v>-6.945071574000003</v>
+        <v>-7.076442828000002</v>
       </c>
       <c r="P83">
-        <v>-26.12669782600001</v>
+        <v>-26.62090397200001</v>
       </c>
       <c r="Q83">
-        <v>-10.72669782600001</v>
+        <v>-11.22090397200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2445223927891612</v>
+        <v>0.2555625257218923</v>
       </c>
       <c r="T83">
-        <v>3.350745031308909</v>
+        <v>3.536897533048292</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07294002249702371</v>
+        <v>0.07205051002754782</v>
       </c>
       <c r="W83">
-        <v>0.2186007426952018</v>
+        <v>0.2188104897355042</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3473334404620178</v>
+        <v>0.3430976667978468</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2254258562130541</v>
+        <v>0.2273258562130541</v>
       </c>
       <c r="C84">
-        <v>-149.1623279230134</v>
+        <v>-152.4309399375957</v>
       </c>
       <c r="D84">
-        <v>59.31367207698664</v>
+        <v>58.69806006240437</v>
       </c>
       <c r="E84">
-        <v>129.246</v>
+        <v>131.8990000000001</v>
       </c>
       <c r="F84">
-        <v>217.546</v>
+        <v>220.199</v>
       </c>
       <c r="G84">
         <v>9.07</v>
@@ -8175,37 +8175,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M84">
-        <v>51.29734680000001</v>
+        <v>51.92292420000001</v>
       </c>
       <c r="N84">
-        <v>-33.69734680000001</v>
+        <v>-34.32292420000002</v>
       </c>
       <c r="O84">
-        <v>-7.076442828000002</v>
+        <v>-7.207814082000003</v>
       </c>
       <c r="P84">
-        <v>-26.62090397200001</v>
+        <v>-27.11511011800001</v>
       </c>
       <c r="Q84">
-        <v>-11.22090397200001</v>
+        <v>-11.71511011800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2555625257218923</v>
+        <v>0.2679014978231801</v>
       </c>
       <c r="T84">
-        <v>3.536897533048292</v>
+        <v>3.744950329109957</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07205051002754782</v>
+        <v>0.07118243159348098</v>
       </c>
       <c r="W84">
-        <v>0.2188104897355042</v>
+        <v>0.2190151826302572</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3430976667978468</v>
+        <v>0.338963959968957</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2273258562130541</v>
+        <v>0.2292258562130541</v>
       </c>
       <c r="C85">
-        <v>-152.4309399375957</v>
+        <v>-155.686904440757</v>
       </c>
       <c r="D85">
-        <v>58.69806006240437</v>
+        <v>58.09509555924302</v>
       </c>
       <c r="E85">
-        <v>131.8990000000001</v>
+        <v>134.552</v>
       </c>
       <c r="F85">
-        <v>220.199</v>
+        <v>222.852</v>
       </c>
       <c r="G85">
         <v>9.07</v>
@@ -8257,37 +8257,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M85">
-        <v>51.92292420000001</v>
+        <v>52.54850160000001</v>
       </c>
       <c r="N85">
-        <v>-34.32292420000002</v>
+        <v>-34.94850160000001</v>
       </c>
       <c r="O85">
-        <v>-7.207814082000003</v>
+        <v>-7.339185336000003</v>
       </c>
       <c r="P85">
-        <v>-27.11511011800001</v>
+        <v>-27.60931626400001</v>
       </c>
       <c r="Q85">
-        <v>-11.71511011800001</v>
+        <v>-12.20931626400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2679014978231801</v>
+        <v>0.281782841437129</v>
       </c>
       <c r="T85">
-        <v>3.744950329109957</v>
+        <v>3.97900972467933</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07118243159348098</v>
+        <v>0.07033502169355858</v>
       </c>
       <c r="W85">
-        <v>0.2190151826302572</v>
+        <v>0.2192150018846589</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.338963959968957</v>
+        <v>0.3349286747312313</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2292258562130541</v>
+        <v>0.2311258562130541</v>
       </c>
       <c r="C86">
-        <v>-155.6869044407569</v>
+        <v>-158.9306072268658</v>
       </c>
       <c r="D86">
-        <v>58.09509555924308</v>
+        <v>57.5043927731342</v>
       </c>
       <c r="E86">
-        <v>134.552</v>
+        <v>137.205</v>
       </c>
       <c r="F86">
-        <v>222.852</v>
+        <v>225.505</v>
       </c>
       <c r="G86">
         <v>9.07</v>
@@ -8339,37 +8339,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M86">
-        <v>52.5485016</v>
+        <v>53.174079</v>
       </c>
       <c r="N86">
-        <v>-34.94850160000001</v>
+        <v>-35.574079</v>
       </c>
       <c r="O86">
-        <v>-7.339185336000002</v>
+        <v>-7.470556590000001</v>
       </c>
       <c r="P86">
-        <v>-27.60931626400001</v>
+        <v>-28.10352241</v>
       </c>
       <c r="Q86">
-        <v>-12.20931626400001</v>
+        <v>-12.70352241</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2817828414371288</v>
+        <v>0.2975150308662707</v>
       </c>
       <c r="T86">
-        <v>3.979009724679327</v>
+        <v>4.244277039657949</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0703350216935586</v>
+        <v>0.06950755085010496</v>
       </c>
       <c r="W86">
-        <v>0.2192150018846589</v>
+        <v>0.2194101195095453</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3349286747312314</v>
+        <v>0.3309883373814523</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2311258562130541</v>
+        <v>0.2330258562130541</v>
       </c>
       <c r="C87">
-        <v>-158.9306072268658</v>
+        <v>-162.1624185574146</v>
       </c>
       <c r="D87">
-        <v>57.5043927731342</v>
+        <v>56.92558144258546</v>
       </c>
       <c r="E87">
-        <v>137.205</v>
+        <v>139.858</v>
       </c>
       <c r="F87">
-        <v>225.505</v>
+        <v>228.158</v>
       </c>
       <c r="G87">
         <v>9.07</v>
@@ -8421,37 +8421,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M87">
-        <v>53.174079</v>
+        <v>53.7996564</v>
       </c>
       <c r="N87">
-        <v>-35.574079</v>
+        <v>-36.19965640000001</v>
       </c>
       <c r="O87">
-        <v>-7.470556590000001</v>
+        <v>-7.601927844000001</v>
       </c>
       <c r="P87">
-        <v>-28.10352241</v>
+        <v>-28.59772855600001</v>
       </c>
       <c r="Q87">
-        <v>-12.70352241</v>
+        <v>-13.19772855600001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2975150308662707</v>
+        <v>0.3154946759281472</v>
       </c>
       <c r="T87">
-        <v>4.244277039657949</v>
+        <v>4.547439685347803</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06950755085010496</v>
+        <v>0.06869932351463863</v>
       </c>
       <c r="W87">
-        <v>0.2194101195095453</v>
+        <v>0.2196006995152482</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3309883373814523</v>
+        <v>0.3271396357839935</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2330258562130541</v>
+        <v>0.2349258562130541</v>
       </c>
       <c r="C88">
-        <v>-162.1624185574146</v>
+        <v>-165.3826939349613</v>
       </c>
       <c r="D88">
-        <v>56.92558144258546</v>
+        <v>56.35830606503869</v>
       </c>
       <c r="E88">
-        <v>139.858</v>
+        <v>142.511</v>
       </c>
       <c r="F88">
-        <v>228.158</v>
+        <v>230.811</v>
       </c>
       <c r="G88">
         <v>9.07</v>
@@ -8503,37 +8503,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M88">
-        <v>53.7996564</v>
+        <v>54.4252338</v>
       </c>
       <c r="N88">
-        <v>-36.19965640000001</v>
+        <v>-36.82523380000001</v>
       </c>
       <c r="O88">
-        <v>-7.601927844000001</v>
+        <v>-7.733299098000001</v>
       </c>
       <c r="P88">
-        <v>-28.59772855600001</v>
+        <v>-29.09193470200001</v>
       </c>
       <c r="Q88">
-        <v>-13.19772855600001</v>
+        <v>-13.69193470200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3154946759281472</v>
+        <v>0.3362404202303124</v>
       </c>
       <c r="T88">
-        <v>4.547439685347803</v>
+        <v>4.897242738066864</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06869932351463863</v>
+        <v>0.06790967611791865</v>
       </c>
       <c r="W88">
-        <v>0.2196006995152482</v>
+        <v>0.2197868983713948</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3271396357839935</v>
+        <v>0.3233794100853269</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2349258562130541</v>
+        <v>0.2368258562130541</v>
       </c>
       <c r="C89">
-        <v>-165.3826939349613</v>
+        <v>-168.5917748312536</v>
       </c>
       <c r="D89">
-        <v>56.35830606503869</v>
+        <v>55.80222516874642</v>
       </c>
       <c r="E89">
-        <v>142.511</v>
+        <v>145.164</v>
       </c>
       <c r="F89">
-        <v>230.811</v>
+        <v>233.464</v>
       </c>
       <c r="G89">
         <v>9.07</v>
@@ -8585,37 +8585,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M89">
-        <v>54.4252338</v>
+        <v>55.05081120000001</v>
       </c>
       <c r="N89">
-        <v>-36.82523380000001</v>
+        <v>-37.45081120000001</v>
       </c>
       <c r="O89">
-        <v>-7.733299098000001</v>
+        <v>-7.864670352000002</v>
       </c>
       <c r="P89">
-        <v>-29.09193470200001</v>
+        <v>-29.58614084800001</v>
       </c>
       <c r="Q89">
-        <v>-13.69193470200001</v>
+        <v>-14.18614084800001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3362404202303124</v>
+        <v>0.3604437885828384</v>
       </c>
       <c r="T89">
-        <v>4.897242738066864</v>
+        <v>5.305346299572437</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06790967611791865</v>
+        <v>0.06713797525294229</v>
       </c>
       <c r="W89">
-        <v>0.2197868983713948</v>
+        <v>0.2199688654353562</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3233794100853269</v>
+        <v>0.31970464406163</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2368258562130541</v>
+        <v>0.2387258562130541</v>
       </c>
       <c r="C90">
-        <v>-168.5917748312536</v>
+        <v>-171.7899893726669</v>
       </c>
       <c r="D90">
-        <v>55.80222516874642</v>
+        <v>55.25701062733314</v>
       </c>
       <c r="E90">
-        <v>145.164</v>
+        <v>147.817</v>
       </c>
       <c r="F90">
-        <v>233.464</v>
+        <v>236.117</v>
       </c>
       <c r="G90">
         <v>9.07</v>
@@ -8667,37 +8667,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M90">
-        <v>55.05081120000001</v>
+        <v>55.67638860000001</v>
       </c>
       <c r="N90">
-        <v>-37.45081120000001</v>
+        <v>-38.07638860000002</v>
       </c>
       <c r="O90">
-        <v>-7.864670352000002</v>
+        <v>-7.996041606000003</v>
       </c>
       <c r="P90">
-        <v>-29.58614084800001</v>
+        <v>-30.08034699400001</v>
       </c>
       <c r="Q90">
-        <v>-14.18614084800001</v>
+        <v>-14.68034699400001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3604437885828384</v>
+        <v>0.3890477693630964</v>
       </c>
       <c r="T90">
-        <v>5.305346299572437</v>
+        <v>5.787650508624476</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06713797525294229</v>
+        <v>0.06638361598043732</v>
       </c>
       <c r="W90">
-        <v>0.2199688654353562</v>
+        <v>0.2201467433518129</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.31970464406163</v>
+        <v>0.3161124570497015</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2387258562130541</v>
+        <v>0.2406258562130541</v>
       </c>
       <c r="C91">
-        <v>-171.7899893726669</v>
+        <v>-174.97765298585</v>
       </c>
       <c r="D91">
-        <v>55.25701062733314</v>
+        <v>54.72234701415005</v>
       </c>
       <c r="E91">
-        <v>147.817</v>
+        <v>150.47</v>
       </c>
       <c r="F91">
-        <v>236.117</v>
+        <v>238.77</v>
       </c>
       <c r="G91">
         <v>9.07</v>
@@ -8749,37 +8749,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M91">
-        <v>55.67638860000001</v>
+        <v>56.30196600000001</v>
       </c>
       <c r="N91">
-        <v>-38.07638860000002</v>
+        <v>-38.70196600000001</v>
       </c>
       <c r="O91">
-        <v>-7.996041606000003</v>
+        <v>-8.127412860000003</v>
       </c>
       <c r="P91">
-        <v>-30.08034699400001</v>
+        <v>-30.57455314000001</v>
       </c>
       <c r="Q91">
-        <v>-14.68034699400001</v>
+        <v>-15.17455314000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3890477693630964</v>
+        <v>0.4233725462994062</v>
       </c>
       <c r="T91">
-        <v>5.787650508624476</v>
+        <v>6.366415559486925</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06638361598043732</v>
+        <v>0.06564602024732136</v>
       </c>
       <c r="W91">
-        <v>0.2201467433518129</v>
+        <v>0.2203206684256816</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3161124570497015</v>
+        <v>0.312600096415816</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2406258562130541</v>
+        <v>0.2425258562130541</v>
       </c>
       <c r="C92">
-        <v>-174.97765298585</v>
+        <v>-178.155069006246</v>
       </c>
       <c r="D92">
-        <v>54.72234701415005</v>
+        <v>54.19793099375399</v>
       </c>
       <c r="E92">
-        <v>150.47</v>
+        <v>153.123</v>
       </c>
       <c r="F92">
-        <v>238.77</v>
+        <v>241.423</v>
       </c>
       <c r="G92">
         <v>9.07</v>
@@ -8831,37 +8831,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M92">
-        <v>56.30196600000001</v>
+        <v>56.92754340000001</v>
       </c>
       <c r="N92">
-        <v>-38.70196600000001</v>
+        <v>-39.32754340000002</v>
       </c>
       <c r="O92">
-        <v>-8.127412860000003</v>
+        <v>-8.258784114000003</v>
       </c>
       <c r="P92">
-        <v>-30.57455314000001</v>
+        <v>-31.06875928600002</v>
       </c>
       <c r="Q92">
-        <v>-15.17455314000001</v>
+        <v>-15.66875928600002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4233725462994062</v>
+        <v>0.4653250514437847</v>
       </c>
       <c r="T92">
-        <v>6.366415559486925</v>
+        <v>7.073795066096584</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06564602024732136</v>
+        <v>0.06492463540943869</v>
       </c>
       <c r="W92">
-        <v>0.2203206684256816</v>
+        <v>0.2204907709704544</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.312600096415816</v>
+        <v>0.3091649305211367</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2425258562130541</v>
+        <v>0.2444258562130541</v>
       </c>
       <c r="C93">
-        <v>-178.155069006246</v>
+        <v>-181.3225292519562</v>
       </c>
       <c r="D93">
-        <v>54.19793099375399</v>
+        <v>53.68347074804388</v>
       </c>
       <c r="E93">
-        <v>153.123</v>
+        <v>155.776</v>
       </c>
       <c r="F93">
-        <v>241.423</v>
+        <v>244.076</v>
       </c>
       <c r="G93">
         <v>9.07</v>
@@ -8913,37 +8913,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M93">
-        <v>56.92754340000001</v>
+        <v>57.55312080000001</v>
       </c>
       <c r="N93">
-        <v>-39.32754340000002</v>
+        <v>-39.95312080000001</v>
       </c>
       <c r="O93">
-        <v>-8.258784114000003</v>
+        <v>-8.390155368000002</v>
       </c>
       <c r="P93">
-        <v>-31.06875928600002</v>
+        <v>-31.56296543200001</v>
       </c>
       <c r="Q93">
-        <v>-15.66875928600002</v>
+        <v>-16.16296543200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4653250514437847</v>
+        <v>0.5177656828742578</v>
       </c>
       <c r="T93">
-        <v>7.073795066096584</v>
+        <v>7.95801944935866</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06492463540943869</v>
+        <v>0.06421893285064045</v>
       </c>
       <c r="W93">
-        <v>0.2204907709704544</v>
+        <v>0.220657175633819</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3091649305211367</v>
+        <v>0.305804442145907</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2444258562130541</v>
+        <v>0.2463258562130541</v>
       </c>
       <c r="C94">
-        <v>-181.3225292519562</v>
+        <v>-184.480314565227</v>
       </c>
       <c r="D94">
-        <v>53.68347074804388</v>
+        <v>53.17868543477297</v>
       </c>
       <c r="E94">
-        <v>155.776</v>
+        <v>158.429</v>
       </c>
       <c r="F94">
-        <v>244.076</v>
+        <v>246.729</v>
       </c>
       <c r="G94">
         <v>9.07</v>
@@ -8995,37 +8995,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M94">
-        <v>57.55312080000001</v>
+        <v>58.17869820000001</v>
       </c>
       <c r="N94">
-        <v>-39.95312080000001</v>
+        <v>-40.57869820000001</v>
       </c>
       <c r="O94">
-        <v>-8.390155368000002</v>
+        <v>-8.521526622000001</v>
       </c>
       <c r="P94">
-        <v>-31.56296543200001</v>
+        <v>-32.05717157800001</v>
       </c>
       <c r="Q94">
-        <v>-16.16296543200001</v>
+        <v>-16.65717157800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5177656828742578</v>
+        <v>0.5851893518562947</v>
       </c>
       <c r="T94">
-        <v>7.95801944935866</v>
+        <v>9.094879370695612</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06421893285064045</v>
+        <v>0.06352840669095615</v>
       </c>
       <c r="W94">
-        <v>0.220657175633819</v>
+        <v>0.2208200017022725</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.305804442145907</v>
+        <v>0.3025162223378864</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2463258562130541</v>
+        <v>0.2482258562130541</v>
       </c>
       <c r="C95">
-        <v>-184.480314565227</v>
+        <v>-187.6286953236732</v>
       </c>
       <c r="D95">
-        <v>53.17868543477297</v>
+        <v>52.68330467632688</v>
       </c>
       <c r="E95">
-        <v>158.429</v>
+        <v>161.0820000000001</v>
       </c>
       <c r="F95">
-        <v>246.729</v>
+        <v>249.382</v>
       </c>
       <c r="G95">
         <v>9.07</v>
@@ -9077,37 +9077,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M95">
-        <v>58.17869820000001</v>
+        <v>58.80427560000001</v>
       </c>
       <c r="N95">
-        <v>-40.57869820000001</v>
+        <v>-41.20427560000002</v>
       </c>
       <c r="O95">
-        <v>-8.521526622000001</v>
+        <v>-8.652897876000003</v>
       </c>
       <c r="P95">
-        <v>-32.05717157800001</v>
+        <v>-32.55137772400001</v>
       </c>
       <c r="Q95">
-        <v>-16.65717157800001</v>
+        <v>-17.15137772400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5851893518562947</v>
+        <v>0.6750875771656774</v>
       </c>
       <c r="T95">
-        <v>9.094879370695612</v>
+        <v>10.61069259914488</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06352840669095615</v>
+        <v>0.06285257257722256</v>
       </c>
       <c r="W95">
-        <v>0.2208200017022725</v>
+        <v>0.2209793633862909</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3025162223378864</v>
+        <v>0.2992979646534408</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2482258562130541</v>
+        <v>0.2501258562130541</v>
       </c>
       <c r="C96">
-        <v>-187.6286953236732</v>
+        <v>-190.7679319231895</v>
       </c>
       <c r="D96">
-        <v>52.68330467632688</v>
+        <v>52.19706807681052</v>
       </c>
       <c r="E96">
-        <v>161.0820000000001</v>
+        <v>163.735</v>
       </c>
       <c r="F96">
-        <v>249.382</v>
+        <v>252.035</v>
       </c>
       <c r="G96">
         <v>9.07</v>
@@ -9159,37 +9159,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M96">
-        <v>58.80427560000001</v>
+        <v>59.42985300000001</v>
       </c>
       <c r="N96">
-        <v>-41.20427560000002</v>
+        <v>-41.82985300000001</v>
       </c>
       <c r="O96">
-        <v>-8.652897876000003</v>
+        <v>-8.784269130000002</v>
       </c>
       <c r="P96">
-        <v>-32.55137772400001</v>
+        <v>-33.04558387000002</v>
       </c>
       <c r="Q96">
-        <v>-17.15137772400001</v>
+        <v>-17.64558387000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6750875771656774</v>
+        <v>0.8009450925988132</v>
       </c>
       <c r="T96">
-        <v>10.61069259914488</v>
+        <v>12.73283111897387</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06285257257722256</v>
+        <v>0.06219096655009391</v>
       </c>
       <c r="W96">
-        <v>0.2209793633862909</v>
+        <v>0.2211353700874878</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2992979646534408</v>
+        <v>0.2961474597623519</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2501258562130541</v>
+        <v>0.2520258562130541</v>
       </c>
       <c r="C97">
-        <v>-190.7679319231895</v>
+        <v>-193.8982752343669</v>
       </c>
       <c r="D97">
-        <v>52.19706807681052</v>
+        <v>51.71972476563317</v>
       </c>
       <c r="E97">
-        <v>163.735</v>
+        <v>166.388</v>
       </c>
       <c r="F97">
-        <v>252.035</v>
+        <v>254.688</v>
       </c>
       <c r="G97">
         <v>9.07</v>
@@ -9241,37 +9241,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M97">
-        <v>59.42985300000001</v>
+        <v>60.05543040000001</v>
       </c>
       <c r="N97">
-        <v>-41.82985300000001</v>
+        <v>-42.45543040000002</v>
       </c>
       <c r="O97">
-        <v>-8.784269130000002</v>
+        <v>-8.915640384000003</v>
       </c>
       <c r="P97">
-        <v>-33.04558387000002</v>
+        <v>-33.53979001600001</v>
       </c>
       <c r="Q97">
-        <v>-17.64558387000002</v>
+        <v>-18.13979001600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8009450925988132</v>
+        <v>0.9897313657485169</v>
       </c>
       <c r="T97">
-        <v>12.73283111897387</v>
+        <v>15.91603889871734</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06219096655009391</v>
+        <v>0.06154314398186377</v>
       </c>
       <c r="W97">
-        <v>0.2211353700874878</v>
+        <v>0.2212881266490765</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2961474597623519</v>
+        <v>0.2930625903898274</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2520258562130541</v>
+        <v>0.2539258562130541</v>
       </c>
       <c r="C98">
-        <v>-193.8982752343668</v>
+        <v>-197.0199670340903</v>
       </c>
       <c r="D98">
-        <v>51.71972476563317</v>
+        <v>51.25103296590972</v>
       </c>
       <c r="E98">
-        <v>166.388</v>
+        <v>169.041</v>
       </c>
       <c r="F98">
-        <v>254.688</v>
+        <v>257.341</v>
       </c>
       <c r="G98">
         <v>9.07</v>
@@ -9323,37 +9323,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M98">
-        <v>60.0554304</v>
+        <v>60.6810078</v>
       </c>
       <c r="N98">
-        <v>-42.4554304</v>
+        <v>-43.08100780000001</v>
       </c>
       <c r="O98">
-        <v>-8.915640384000001</v>
+        <v>-9.047011638000001</v>
       </c>
       <c r="P98">
-        <v>-33.539790016</v>
+        <v>-34.03399616200001</v>
       </c>
       <c r="Q98">
-        <v>-18.13979001600001</v>
+        <v>-18.63399616200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9897313657485145</v>
+        <v>1.304375154331353</v>
       </c>
       <c r="T98">
-        <v>15.9160388987173</v>
+        <v>21.22138519828973</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06154314398186378</v>
+        <v>0.06090867857998888</v>
       </c>
       <c r="W98">
-        <v>0.2212881266490765</v>
+        <v>0.2214377335908387</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2930625903898275</v>
+        <v>0.2900413265713756</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2539258562130541</v>
+        <v>0.2558258562130541</v>
       </c>
       <c r="C99">
-        <v>-197.0199670340903</v>
+        <v>-200.1332404138813</v>
       </c>
       <c r="D99">
-        <v>51.25103296590972</v>
+        <v>50.79075958611872</v>
       </c>
       <c r="E99">
-        <v>169.041</v>
+        <v>171.694</v>
       </c>
       <c r="F99">
-        <v>257.341</v>
+        <v>259.994</v>
       </c>
       <c r="G99">
         <v>9.07</v>
@@ -9405,37 +9405,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M99">
-        <v>60.6810078</v>
+        <v>61.30658520000001</v>
       </c>
       <c r="N99">
-        <v>-43.08100780000001</v>
+        <v>-43.70658520000001</v>
       </c>
       <c r="O99">
-        <v>-9.047011638000001</v>
+        <v>-9.178382892000002</v>
       </c>
       <c r="P99">
-        <v>-34.03399616200001</v>
+        <v>-34.52820230800001</v>
       </c>
       <c r="Q99">
-        <v>-18.63399616200001</v>
+        <v>-19.12820230800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.304375154331353</v>
+        <v>1.933662731497029</v>
       </c>
       <c r="T99">
-        <v>21.22138519828973</v>
+        <v>31.8320777974346</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06090867857998888</v>
+        <v>0.06028716145162166</v>
       </c>
       <c r="W99">
-        <v>0.2214377335908387</v>
+        <v>0.2215842873297076</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2900413265713756</v>
+        <v>0.2870817211981983</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2558258562130541</v>
+        <v>0.257725856213054</v>
       </c>
       <c r="C100">
-        <v>-200.1332404138813</v>
+        <v>-203.2383201664323</v>
       </c>
       <c r="D100">
-        <v>50.79075958611872</v>
+        <v>50.3386798335677</v>
       </c>
       <c r="E100">
-        <v>171.694</v>
+        <v>174.347</v>
       </c>
       <c r="F100">
-        <v>259.994</v>
+        <v>262.647</v>
       </c>
       <c r="G100">
         <v>9.07</v>
@@ -9487,37 +9487,37 @@
         <v>17.59999999999999</v>
       </c>
       <c r="M100">
-        <v>61.30658520000001</v>
+        <v>61.9321626</v>
       </c>
       <c r="N100">
-        <v>-43.70658520000001</v>
+        <v>-44.3321626</v>
       </c>
       <c r="O100">
-        <v>-9.178382892000002</v>
+        <v>-9.309754146000001</v>
       </c>
       <c r="P100">
-        <v>-34.52820230800001</v>
+        <v>-35.022408454</v>
       </c>
       <c r="Q100">
-        <v>-19.12820230800001</v>
+        <v>-19.622408454</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.933662731497029</v>
+        <v>3.821525462994058</v>
       </c>
       <c r="T100">
-        <v>31.8320777974346</v>
+        <v>63.66415559486919</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06028716145162166</v>
+        <v>0.05967820022483761</v>
       </c>
       <c r="W100">
-        <v>0.2215842873297076</v>
+        <v>0.2217278803869833</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2870817211981983</v>
+        <v>0.28418190583256</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.257725856213054</v>
-      </c>
-      <c r="C101">
-        <v>-203.2383201664323</v>
-      </c>
-      <c r="D101">
-        <v>50.3386798335677</v>
-      </c>
-      <c r="E101">
-        <v>174.347</v>
-      </c>
-      <c r="F101">
-        <v>262.647</v>
-      </c>
-      <c r="G101">
-        <v>9.07</v>
-      </c>
-      <c r="H101">
-        <v>177</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.99999999999999</v>
-      </c>
-      <c r="K101">
-        <v>15.4</v>
-      </c>
-      <c r="L101">
-        <v>17.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>61.9321626</v>
-      </c>
-      <c r="N101">
-        <v>-44.3321626</v>
-      </c>
-      <c r="O101">
-        <v>-9.309754146000001</v>
-      </c>
-      <c r="P101">
-        <v>-35.022408454</v>
-      </c>
-      <c r="Q101">
-        <v>-19.622408454</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.821525462994058</v>
-      </c>
-      <c r="T101">
-        <v>63.66415559486919</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05967820022483761</v>
-      </c>
-      <c r="W101">
-        <v>0.2217278803869833</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.28418190583256</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
